--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22663,7 +22663,7 @@
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>SECI000249</t>
+          <t>SECI000258</t>
         </is>
       </c>
       <c r="B2" s="37" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="E2" s="37" t="inlineStr">
         <is>
-          <t>SECI/C&amp;P/IPP/13/0002/26-27</t>
+          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
         </is>
       </c>
       <c r="F2" s="37" t="inlineStr">
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="G2" s="274" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H2" s="37" t="inlineStr">
         <is>
@@ -22700,11 +22700,11 @@
         </is>
       </c>
       <c r="I2" s="37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="37" t="inlineStr">
         <is>
-          <t>Assured peak supply under CfD</t>
+          <t>Assured peak supply</t>
         </is>
       </c>
       <c r="K2" s="274" t="n"/>
@@ -22719,11 +22719,11 @@
         </is>
       </c>
       <c r="N2" s="280" t="n">
-        <v>46237.75</v>
+        <v>46241.75</v>
       </c>
       <c r="O2" s="280" t="n"/>
       <c r="P2" s="280" t="n">
-        <v>46240.41666666666</v>
+        <v>46246.41666666666</v>
       </c>
       <c r="Q2" s="280" t="inlineStr">
         <is>
@@ -22734,17 +22734,17 @@
         <v>46236</v>
       </c>
       <c r="S2" s="37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T2" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tenders/</t>
+          <t>https://www.seci.co.in/tender-details/Ymd_</t>
         </is>
       </c>
       <c r="U2" s="37" t="n"/>
       <c r="V2" s="37" t="inlineStr">
         <is>
-          <t>1000 MWh = 500 MW x 2 hours</t>
+          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
         </is>
       </c>
       <c r="W2" s="278">
@@ -22764,7 +22764,7 @@
         <v/>
       </c>
       <c r="AA2">
-        <f>IF(A2="","",C2&amp;"|"&amp;E2&amp;"|"&amp;TEXT(N2,"yyyymmdd")&amp;"|"&amp;Q2&amp;"|"&amp;S2&amp;"|"&amp;TEXT(AI2,"yyyymmdd"))</f>
+        <f>IF(A3="","",C3&amp;"|"&amp;E3&amp;"|"&amp;TEXT(N3,"yyyymmdd")&amp;"|"&amp;Q3&amp;"|"&amp;S3&amp;"|"&amp;TEXT(AI3,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB2" s="281" t="n">
@@ -22781,62 +22781,64 @@
         </is>
       </c>
       <c r="AE2" s="281">
-        <f>IF(A2="","",IF(AC2="Official agency page",3,IF(AC2="Official government portal",3,IF(AC2="Official tender document",4,1)))+IF(AD2="Core fields",2,1))</f>
+        <f>IF(A3="","",IF(AC3="Official agency page",3,IF(AC3="Official government portal",3,IF(AC3="Official tender document",4,1)))+IF(AD3="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF2" s="281">
-        <f>IF(A2="","",IF(OR(Q2="Open",Q2="Extended"),"Current Opportunity",IF(Q2="Corrigendum","Needs Status Check",IF(Q2="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A3="","",IF(OR(Q3="Open",Q3="Extended"),"Current Opportunity",IF(Q3="Corrigendum","Needs Status Check",IF(Q3="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG2" s="281" t="n">
-        <v>46131</v>
+        <v>46178</v>
       </c>
       <c r="AH2" s="281" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AI2" s="281" t="n">
-        <v>46220</v>
+          <t xml:space="preserve"> ; -; 0; 2; 6; 7; 8; ;</t>
+        </is>
+      </c>
+      <c r="AI2" s="281" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Amendment-01 uploaded 17-Jul-2026; revised RfS dated 15-Jul-2026</t>
+          <t>Amendment-01 uploaded 08-Jul-2026</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Contract for Difference (CfD); power sold through exchanges</t>
+          <t>Tariff-based competitive bidding with PPA/PSA</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>RPD chooses any 2 hours daily between 18:00 and 24:00, within non-solar hours</t>
+          <t>Buying Entity selects 4 hours daily across evening-to-next-morning non-solar peak hours; at least one continuous hour</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2 MWh per MW contracted capacity per day; for 500 MW = 1,000 MWh/day</t>
+          <t>4 MWh per MW contracted capacity per day; for 1,200 MW = 4,800 MWh/day</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>No monthly PLF stated. Performance tested weekly; penalties recovered monthly</t>
+          <t>Monthly reconciliation. Minimum effective supply = 90% of monthly scheduled peak-energy requirement before penalty applies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>100% of annual scheduled energy must be renewable. No annual PLF/CUF percentage stated</t>
+          <t>100% annual offered energy must be renewable. No annual PLF/CUF percentage stated</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Up to 10% weekly shortfall permitted; minimum 90% of 14 MWh/MW per contract week</t>
+          <t>Monthly shortfall up to 10% below required peak energy permitted</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Beyond 10% weekly shortfall: 1.5 × [highest applicable exchange MCP during non-solar hours minus strike price] × shortfall; no penalty when reference rate is below strike price; no CfD settlement for shortfall</t>
+          <t>Shortfall beyond 10% monthly: 1.5 × PPA tariff × energy shortfall</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -22846,37 +22848,42 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Up to 25% of total annual required energy</t>
+          <t>Up to 5% of total annual required energy</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>External RE can directly meet peak supply or charge ESS. Charging energy is not counted; only discharged energy counts. External-energy excess above 25% receives no CfD settlement</t>
+          <t>External RE may directly meet peak requirements or charge ESS. Only discharged ESS energy counts toward the 5%; excess above 5% is unpaid and excluded from performance</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>ESS may be used for merchant/third-party or exchange sale after completing the day’s 2 MWh/MW peak obligation; premature merchant sale attracts an additional penalty</t>
+          <t>ESS may be used outside peak hours for third-party/exchange sale after PPA obligations. Sale before fulfilling obligations attracts 1.5 × highest DAM/GDAM/RTM market rate per kWh, in addition to shortfall penalty</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/uploads/tenders/Revised_RfS_for_1000_MWh_assured_Peak_Supply_under_CfD_Mechanism_%28CfD-I%29.pdf</t>
+          <t>https://www.seci.co.in/uploads/tenders/RfS_for_4800_MWh_Peak_Supply_%28FDRE-IX%29-_final_upload.pdf</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Verified from revised official RfS</t>
+          <t>Verified from official RfS; latest SECI page shows revised bid dates</t>
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>SECI000258</t>
+          <t>SJVN-BESS2</t>
         </is>
       </c>
       <c r="B3" s="37" t="inlineStr">
@@ -22886,26 +22893,26 @@
       </c>
       <c r="C3" s="37" t="inlineStr">
         <is>
-          <t>SECI</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="D3" s="37" t="inlineStr">
         <is>
-          <t>All India</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E3" s="37" t="inlineStr">
         <is>
-          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
+          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>FDRE</t>
+          <t>BESS</t>
         </is>
       </c>
       <c r="G3" s="274" t="n">
-        <v>1500</v>
+        <v>265</v>
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
@@ -22913,31 +22920,25 @@
         </is>
       </c>
       <c r="I3" s="37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="37" t="inlineStr">
         <is>
-          <t>Assured peak supply</t>
+          <t>Standalone BESS under VGF and TBCB</t>
         </is>
       </c>
       <c r="K3" s="274" t="n"/>
-      <c r="L3" s="37" t="inlineStr">
+      <c r="L3" s="37" t="n"/>
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>As per RfS</t>
         </is>
       </c>
-      <c r="M3" s="37" t="inlineStr">
-        <is>
-          <t>As per RfS</t>
-        </is>
-      </c>
       <c r="N3" s="280" t="n">
-        <v>46241.75</v>
+        <v>46255</v>
       </c>
       <c r="O3" s="280" t="n"/>
-      <c r="P3" s="280" t="n">
-        <v>46246.41666666666</v>
-      </c>
+      <c r="P3" s="280" t="n"/>
       <c r="Q3" s="280" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22947,17 +22948,17 @@
         <v>46236</v>
       </c>
       <c r="S3" s="37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T3" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tender-details/Ymd_</t>
+          <t>https://sjvn.nic.in/en/tender</t>
         </is>
       </c>
       <c r="U3" s="37" t="n"/>
       <c r="V3" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
+          <t>265 MW / 530 MWh BESS in Haryana</t>
         </is>
       </c>
       <c r="W3" s="278">
@@ -22977,7 +22978,7 @@
         <v/>
       </c>
       <c r="AA3">
-        <f>IF(A3="","",C3&amp;"|"&amp;E3&amp;"|"&amp;TEXT(N3,"yyyymmdd")&amp;"|"&amp;Q3&amp;"|"&amp;S3&amp;"|"&amp;TEXT(AI3,"yyyymmdd"))</f>
+        <f>IF(A4="","",C4&amp;"|"&amp;E4&amp;"|"&amp;TEXT(N4,"yyyymmdd")&amp;"|"&amp;Q4&amp;"|"&amp;S4&amp;"|"&amp;TEXT(AI4,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB3" s="281" t="n">
@@ -22994,129 +22995,116 @@
         </is>
       </c>
       <c r="AE3" s="281">
-        <f>IF(A3="","",IF(AC3="Official agency page",3,IF(AC3="Official government portal",3,IF(AC3="Official tender document",4,1)))+IF(AD3="Core fields",2,1))</f>
+        <f>IF(A4="","",IF(AC4="Official agency page",3,IF(AC4="Official government portal",3,IF(AC4="Official tender document",4,1)))+IF(AD4="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF3" s="281">
-        <f>IF(A3="","",IF(OR(Q3="Open",Q3="Extended"),"Current Opportunity",IF(Q3="Corrigendum","Needs Status Check",IF(Q3="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A4="","",IF(OR(Q4="Open",Q4="Extended"),"Current Opportunity",IF(Q4="Corrigendum","Needs Status Check",IF(Q4="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG3" s="281" t="n">
-        <v>46178</v>
-      </c>
-      <c r="AH3" s="281" t="inlineStr">
-        <is>
-          <t>-; 0; 2; 6; 7; 8</t>
-        </is>
-      </c>
-      <c r="AI3" s="281" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+        <v>46227</v>
+      </c>
+      <c r="AH3" s="281" t="n"/>
+      <c r="AI3" s="281" t="n"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Amendment-01 uploaded 08-Jul-2026</t>
+          <t>No corrigendum identified in the captured official listing.</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Tariff-based competitive bidding with PPA/PSA</t>
+          <t>Standalone BESS under VGF and tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Buying Entity selects 4 hours daily across evening-to-next-morning non-solar peak hours; at least one continuous hour</t>
+          <t>Dispatch schedule and availability obligations governed by RfS/BESSA/BESPA</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4 MWh per MW contracted capacity per day; for 1,200 MW = 4,800 MWh/day</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Monthly reconciliation. Minimum effective supply = 90% of monthly scheduled peak-energy requirement before penalty applies</t>
+          <t>PLF is not applicable to standalone BESS; monthly availability/energy obligations require document review</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>100% annual offered energy must be renewable. No annual PLF/CUF percentage stated</t>
+          <t>Annual PLF/CUF not applicable; annual availability/cycle obligations require document review</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Monthly shortfall up to 10% below required peak energy permitted</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Shortfall beyond 10% monthly: 1.5 × PPA tariff × energy shortfall</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Yes — green-market sources or bilateral RE agreements permitted</t>
+          <t>Charging-source provision not verified from accessible document text</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Up to 5% of total annual required energy</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>External RE may directly meet peak requirements or charge ESS. Only discharged ESS energy counts toward the 5%; excess above 5% is unpaid and excluded from performance</t>
+          <t>Official RfS PDF was listed but could not be reliably fetched in this review</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ESS may be used outside peak hours for third-party/exchange sale after PPA obligations. Sale before fulfilling obligations attracts 1.5 × highest DAM/GDAM/RTM market rate per kWh, in addition to shortfall penalty</t>
+          <t>Merchant-use rights not verified</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/uploads/tenders/RfS_for_4800_MWh_Peak_Supply_%28FDRE-IX%29-_final_upload.pdf</t>
+          <t>https://sjvn.nic.in/sites/default/files/2026-07/RfS%20BESS%202%20240726.pdf</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Verified from official RfS; latest SECI page shows revised bid dates</t>
+          <t>Document-level review pending; no assumptions inserted</t>
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46237.26024921522</v>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
-        </is>
+        <v>46238.24191874108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>SJVN-BESS2</t>
+          <t>MSEDCL-BESS-2000</t>
         </is>
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>MSEDCL</t>
         </is>
       </c>
       <c r="D4" s="37" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
+          <t>RfS-2000MW-4000MWh-BESS-2026</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
@@ -23125,7 +23113,7 @@
         </is>
       </c>
       <c r="G4" s="274" t="n">
-        <v>265</v>
+        <v>2000</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
@@ -23137,7 +23125,7 @@
       </c>
       <c r="J4" s="37" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and TBCB</t>
+          <t>Tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="K4" s="274" t="n"/>
@@ -23147,31 +23135,29 @@
           <t>As per RfS</t>
         </is>
       </c>
-      <c r="N4" s="280" t="n">
-        <v>46255</v>
-      </c>
+      <c r="N4" s="280" t="n"/>
       <c r="O4" s="280" t="n"/>
       <c r="P4" s="280" t="n"/>
       <c r="Q4" s="280" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Corrigendum</t>
         </is>
       </c>
       <c r="R4" s="280" t="n">
         <v>46236</v>
       </c>
       <c r="S4" s="37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4" s="37" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/en/tender</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="U4" s="37" t="n"/>
       <c r="V4" s="37" t="inlineStr">
         <is>
-          <t>265 MW / 530 MWh BESS in Haryana</t>
+          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
         </is>
       </c>
       <c r="W4" s="278">
@@ -23191,7 +23177,7 @@
         <v/>
       </c>
       <c r="AA4">
-        <f>IF(A4="","",C4&amp;"|"&amp;E4&amp;"|"&amp;TEXT(N4,"yyyymmdd")&amp;"|"&amp;Q4&amp;"|"&amp;S4&amp;"|"&amp;TEXT(AI4,"yyyymmdd"))</f>
+        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB4" s="281" t="n">
@@ -23204,65 +23190,71 @@
       </c>
       <c r="AD4" s="281" t="inlineStr">
         <is>
-          <t>Core fields</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="AE4" s="281">
-        <f>IF(A4="","",IF(AC4="Official agency page",3,IF(AC4="Official government portal",3,IF(AC4="Official tender document",4,1)))+IF(AD4="Core fields",2,1))</f>
+        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF4" s="281">
-        <f>IF(A4="","",IF(OR(Q4="Open",Q4="Extended"),"Current Opportunity",IF(Q4="Corrigendum","Needs Status Check",IF(Q4="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG4" s="281" t="n">
-        <v>46227</v>
-      </c>
-      <c r="AH4" s="281" t="n"/>
-      <c r="AI4" s="281" t="n"/>
+        <v>46203</v>
+      </c>
+      <c r="AH4" s="281" t="inlineStr">
+        <is>
+          <t>2026-07-07; 2026-07-22</t>
+        </is>
+      </c>
+      <c r="AI4" s="281" t="n">
+        <v>46225</v>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>No corrigendum identified in the captured official listing.</t>
+          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and tariff-based competitive bidding</t>
+          <t>Standalone BESS under tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Dispatch schedule and availability obligations governed by RfS/BESSA/BESPA</t>
+          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>PLF is not applicable to standalone BESS; monthly availability/energy obligations require document review</t>
+          <t>Monthly availability/payment condition not verified from accessible current document text</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Annual PLF/CUF not applicable; annual availability/cycle obligations require document review</t>
+          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Charging-source provision not verified from accessible document text</t>
+          <t>Charging source and grid/exchange charging permission not verified</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -23272,7 +23264,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Official RfS PDF was listed but could not be reliably fetched in this review</t>
+          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -23282,95 +23274,81 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/sites/default/files/2026-07/RfS%20BESS%202%20240726.pdf</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Document-level review pending; no assumptions inserted</t>
+          <t>Tender confirmed; commercial clause extraction pending</t>
         </is>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL-BESS-2000</t>
+          <t>SECI000240</t>
         </is>
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL</t>
-        </is>
-      </c>
-      <c r="D5" s="37" t="inlineStr">
-        <is>
-          <t>Maharashtra</t>
-        </is>
-      </c>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="n"/>
       <c r="E5" s="37" t="inlineStr">
         <is>
-          <t>RfS-2000MW-4000MWh-BESS-2026</t>
+          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>FDRE</t>
         </is>
       </c>
       <c r="G5" s="274" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="37" t="inlineStr">
-        <is>
-          <t>Tariff-based competitive bidding</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="n"/>
+      <c r="J5" s="37" t="n"/>
       <c r="K5" s="274" t="n"/>
       <c r="L5" s="37" t="n"/>
-      <c r="M5" s="37" t="inlineStr">
-        <is>
-          <t>As per RfS</t>
-        </is>
-      </c>
+      <c r="M5" s="37" t="n"/>
       <c r="N5" s="280" t="n"/>
       <c r="O5" s="280" t="n"/>
       <c r="P5" s="280" t="n"/>
       <c r="Q5" s="280" t="inlineStr">
         <is>
-          <t>Corrigendum</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46236</v>
+        <v>46237.26024921297</v>
       </c>
       <c r="S5" s="37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
+          <t>https://www.seci.co.in/tender-details/YmZ3</t>
         </is>
       </c>
       <c r="U5" s="37" t="n"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
+          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
         </is>
       </c>
       <c r="W5" s="278">
@@ -23389,145 +23367,55 @@
         <f>IF(Y5="","",IF(COUNTIF($Y$2:$Y$501,Y5)&gt;1,"Duplicate","Unique"))</f>
         <v/>
       </c>
-      <c r="AA5">
-        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="281" t="n">
-        <v>46236</v>
-      </c>
+      <c r="AB5" s="281" t="n"/>
       <c r="AC5" s="281" t="inlineStr">
         <is>
           <t>Official agency page</t>
         </is>
       </c>
-      <c r="AD5" s="281" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="AE5" s="281">
-        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="281">
-        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="281" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AH5" s="281" t="inlineStr">
-        <is>
-          <t>2026-07-07; 2026-07-22</t>
-        </is>
-      </c>
-      <c r="AI5" s="281" t="n">
-        <v>46225</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Standalone BESS under tariff-based competitive bidding</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Monthly availability/payment condition not verified from accessible current document text</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>Charging source and grid/exchange charging permission not verified</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Merchant-use rights not verified</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Tender confirmed; commercial clause extraction pending</t>
-        </is>
+      <c r="AD5" s="281" t="n"/>
+      <c r="AE5" s="281" t="n"/>
+      <c r="AF5" s="281" t="n"/>
+      <c r="AG5" s="281" t="n"/>
+      <c r="AH5" s="281" t="inlineStr"/>
+      <c r="AI5" s="281" t="n"/>
+      <c r="AX5" s="282" t="n">
+        <v>46237.26024921297</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>SECI000240</t>
-        </is>
-      </c>
+      <c r="A6" s="37" t="n"/>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>SECI</t>
+          <t>GRIDCO</t>
         </is>
       </c>
       <c r="D6" s="37" t="n"/>
       <c r="E6" s="37" t="inlineStr">
         <is>
-          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
+          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>FDRE</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="G6" s="274" t="n">
-        <v>1000</v>
+        <v>225</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
@@ -23548,18 +23436,18 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tender-details/YmZ3</t>
+          <t>https://www.gridco.co.in/tender.aspx</t>
         </is>
       </c>
       <c r="U6" s="37" t="inlineStr"/>
       <c r="V6" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
+          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23591,14 +23479,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
         </is>
       </c>
     </row>
@@ -23617,7 +23505,7 @@
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
+          <t>Scope of Work :</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
@@ -23647,7 +23535,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23658,7 +23546,7 @@
       <c r="U7" s="37" t="inlineStr"/>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W7" s="278">
@@ -23690,48 +23578,26 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
+          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n"/>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>Odisha</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>GRIDCO</t>
-        </is>
-      </c>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
       <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>Scope of Work :</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="G8" s="274" t="n">
-        <v>225</v>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="274" t="n"/>
+      <c r="H8" s="37" t="n"/>
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="274" t="n"/>
@@ -23740,65 +23606,23 @@
       <c r="N8" s="280" t="n"/>
       <c r="O8" s="280" t="n"/>
       <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R8" s="280" t="n">
-        <v>46237.26024921522</v>
-      </c>
+      <c r="Q8" s="280" t="n"/>
+      <c r="R8" s="280" t="n"/>
       <c r="S8" s="37" t="n"/>
-      <c r="T8" s="37" t="inlineStr">
-        <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
-        </is>
-      </c>
-      <c r="U8" s="37" t="inlineStr"/>
-      <c r="V8" s="37" t="inlineStr">
-        <is>
-          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
-        </is>
-      </c>
-      <c r="W8" s="278">
-        <f>IF(N8="","",N8-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>IF(W8="","",IF(W8&lt;0,"Expired",IF(W8&lt;=3,"Urgent",IF(W8&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>UPPER(TRIM(C8&amp;"|"&amp;E8))</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>IF(Y8="","",IF(COUNTIF($Y$2:$Y$501,Y8)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="T8" s="37" t="n"/>
+      <c r="U8" s="37" t="n"/>
+      <c r="V8" s="37" t="n"/>
+      <c r="W8" s="278" t="n"/>
       <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC8" s="281" t="n"/>
       <c r="AD8" s="281" t="n"/>
       <c r="AE8" s="281" t="n"/>
       <c r="AF8" s="281" t="n"/>
       <c r="AG8" s="281" t="n"/>
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
-      <c r="AX8" s="282" t="n">
-        <v>46237.26024921522</v>
-      </c>
-      <c r="AY8" s="282" t="n">
-        <v>46237.26024921522</v>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
-        </is>
-      </c>
+      <c r="AX8" s="282" t="n"/>
+      <c r="AY8" s="282" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n"/>
@@ -42015,7 +41839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="64" min="1" max="1"/>
@@ -43321,17 +43145,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:AJ2"/>
@@ -43687,7 +43500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -44837,13 +44650,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -44869,7 +44680,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -44902,7 +44712,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -44931,6 +44740,343 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>88</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>25</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SECI000249</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/13/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FDRE</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>500</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Deadline expired without verified extension</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tenders/</t>
         </is>
       </c>
     </row>
@@ -47373,7 +47519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J505"/>
+  <dimension ref="A1:J506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -47589,7 +47735,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46238.24191874108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -49595,15 +49741,36 @@
         </is>
       </c>
       <c r="G505" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46237.26024921297</v>
       </c>
       <c r="H505" s="282" t="n">
-        <v>46237.26024921522</v>
+        <v>46237.26024921297</v>
       </c>
       <c r="I505" t="n">
         <v>7</v>
       </c>
       <c r="J505" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>RUN-20260804054821</t>
+        </is>
+      </c>
+      <c r="G506" s="282" t="n">
+        <v>46238.24191874108</v>
+      </c>
+      <c r="H506" s="282" t="n">
+        <v>46238.24191874108</v>
+      </c>
+      <c r="I506" t="n">
+        <v>6</v>
+      </c>
+      <c r="J506" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
     </row>
     <row r="4">
@@ -23283,7 +23283,7 @@
         </is>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
     </row>
     <row r="5">
@@ -23377,13 +23377,13 @@
       <c r="AE5" s="281" t="n"/>
       <c r="AF5" s="281" t="n"/>
       <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="inlineStr"/>
+      <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
         <v>46237.26024921297</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23479,10 +23479,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23578,10 +23578,10 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -44975,7 +44975,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45008,7 +45007,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45077,6 +45075,335 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>https://www.seci.co.in/tenders/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>88</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>25</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>600</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29990</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
       </c>
     </row>
@@ -47519,7 +47846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J506"/>
+  <dimension ref="A1:J507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -47735,7 +48062,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46239.24097942355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -49762,15 +50089,36 @@
         </is>
       </c>
       <c r="G506" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46238.24191873843</v>
       </c>
       <c r="H506" s="282" t="n">
-        <v>46238.24191874108</v>
+        <v>46238.24191873843</v>
       </c>
       <c r="I506" t="n">
         <v>6</v>
       </c>
       <c r="J506" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>RUN-20260805054700</t>
+        </is>
+      </c>
+      <c r="G507" s="282" t="n">
+        <v>46239.24097942355</v>
+      </c>
+      <c r="H507" s="282" t="n">
+        <v>46239.24097942355</v>
+      </c>
+      <c r="I507" t="n">
+        <v>6</v>
+      </c>
+      <c r="J507" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
     </row>
     <row r="4">
@@ -23283,7 +23283,7 @@
         </is>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
     </row>
     <row r="5">
@@ -23383,7 +23383,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23395,27 +23395,23 @@
       <c r="A6" s="37" t="n"/>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>GRIDCO</t>
+          <t>NTPC REL</t>
         </is>
       </c>
       <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
-        </is>
-      </c>
+      <c r="E6" s="37" t="inlineStr"/>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G6" s="274" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
@@ -23436,18 +23432,18 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
         <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
         </is>
       </c>
       <c r="U6" s="37" t="inlineStr"/>
       <c r="V6" s="37" t="inlineStr">
         <is>
-          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23479,14 +23475,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
+          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
         </is>
       </c>
     </row>
@@ -23505,7 +23501,7 @@
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>Scope of Work :</t>
+          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
@@ -23535,7 +23531,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23546,7 +23542,7 @@
       <c r="U7" s="37" t="inlineStr"/>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W7" s="278">
@@ -23578,26 +23574,48 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
+          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n"/>
-      <c r="B8" s="37" t="n"/>
-      <c r="C8" s="37" t="n"/>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
       <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="274" t="n"/>
-      <c r="H8" s="37" t="n"/>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Scope of Work :</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="G8" s="274" t="n">
+        <v>225</v>
+      </c>
+      <c r="H8" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="274" t="n"/>
@@ -23606,23 +23624,65 @@
       <c r="N8" s="280" t="n"/>
       <c r="O8" s="280" t="n"/>
       <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="n"/>
-      <c r="R8" s="280" t="n"/>
+      <c r="Q8" s="280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R8" s="280" t="n">
+        <v>46240.24317934538</v>
+      </c>
       <c r="S8" s="37" t="n"/>
-      <c r="T8" s="37" t="n"/>
-      <c r="U8" s="37" t="n"/>
-      <c r="V8" s="37" t="n"/>
-      <c r="W8" s="278" t="n"/>
+      <c r="T8" s="37" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/tender.aspx</t>
+        </is>
+      </c>
+      <c r="U8" s="37" t="inlineStr"/>
+      <c r="V8" s="37" t="inlineStr">
+        <is>
+          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+        </is>
+      </c>
+      <c r="W8" s="278">
+        <f>IF(N8="","",N8-TODAY())</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>IF(W8="","",IF(W8&lt;0,"Expired",IF(W8&lt;=3,"Urgent",IF(W8&lt;=7,"Due in 7 Days","Normal"))))</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>UPPER(TRIM(C8&amp;"|"&amp;E8))</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>IF(Y8="","",IF(COUNTIF($Y$2:$Y$501,Y8)&gt;1,"Duplicate","Unique"))</f>
+        <v/>
+      </c>
       <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="n"/>
+      <c r="AC8" s="281" t="inlineStr">
+        <is>
+          <t>Official agency page</t>
+        </is>
+      </c>
       <c r="AD8" s="281" t="n"/>
       <c r="AE8" s="281" t="n"/>
       <c r="AF8" s="281" t="n"/>
       <c r="AG8" s="281" t="n"/>
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
-      <c r="AX8" s="282" t="n"/>
-      <c r="AY8" s="282" t="n"/>
+      <c r="AX8" s="282" t="n">
+        <v>46240.24317934538</v>
+      </c>
+      <c r="AY8" s="282" t="n">
+        <v>46240.24317934538</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n"/>
@@ -43500,7 +43560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -45310,13 +45370,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Solar</t>
@@ -45342,7 +45400,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45375,7 +45432,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45402,6 +45458,335 @@
         </is>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>88</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>600</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29990</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -47846,7 +48231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J507"/>
+  <dimension ref="A1:J508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -48062,7 +48447,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46240.24317934538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -50110,15 +50495,36 @@
         </is>
       </c>
       <c r="G507" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46239.24097942129</v>
       </c>
       <c r="H507" s="282" t="n">
-        <v>46239.24097942355</v>
+        <v>46239.24097942129</v>
       </c>
       <c r="I507" t="n">
         <v>6</v>
       </c>
       <c r="J507" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>RUN-20260806055010</t>
+        </is>
+      </c>
+      <c r="G508" s="282" t="n">
+        <v>46240.24317934538</v>
+      </c>
+      <c r="H508" s="282" t="n">
+        <v>46240.24317934538</v>
+      </c>
+      <c r="I508" t="n">
+        <v>7</v>
+      </c>
+      <c r="J508" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
     </row>
     <row r="4">
@@ -23283,7 +23283,7 @@
         </is>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
     </row>
     <row r="5">
@@ -23383,7 +23383,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23475,10 +23475,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23574,10 +23574,10 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         </is>
       </c>
       <c r="R8" s="280" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="S8" s="37" t="n"/>
       <c r="T8" s="37" t="inlineStr">
@@ -23673,10 +23673,10 @@
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
       <c r="AX8" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AY8" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -45695,13 +45695,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Solar</t>
@@ -45727,7 +45725,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45760,7 +45757,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -45787,6 +45783,375 @@
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>88</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>40</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>25</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>813</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29985</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -48231,7 +48596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J508"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -48447,7 +48812,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46241.20385158412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -50516,15 +50881,36 @@
         </is>
       </c>
       <c r="G508" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46240.24317934028</v>
       </c>
       <c r="H508" s="282" t="n">
-        <v>46240.24317934538</v>
+        <v>46240.24317934028</v>
       </c>
       <c r="I508" t="n">
         <v>7</v>
       </c>
       <c r="J508" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>RUN-20260807045332</t>
+        </is>
+      </c>
+      <c r="G509" s="282" t="n">
+        <v>46241.20385158412</v>
+      </c>
+      <c r="H509" s="282" t="n">
+        <v>46241.20385158412</v>
+      </c>
+      <c r="I509" t="n">
+        <v>7</v>
+      </c>
+      <c r="J509" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22663,7 +22663,7 @@
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>SECI000258</t>
+          <t>SJVN-BESS2</t>
         </is>
       </c>
       <c r="B2" s="37" t="inlineStr">
@@ -22673,26 +22673,26 @@
       </c>
       <c r="C2" s="37" t="inlineStr">
         <is>
-          <t>SECI</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="D2" s="37" t="inlineStr">
         <is>
-          <t>All India</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E2" s="37" t="inlineStr">
         <is>
-          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
+          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
         </is>
       </c>
       <c r="F2" s="37" t="inlineStr">
         <is>
-          <t>FDRE</t>
+          <t>BESS</t>
         </is>
       </c>
       <c r="G2" s="274" t="n">
-        <v>1500</v>
+        <v>265</v>
       </c>
       <c r="H2" s="37" t="inlineStr">
         <is>
@@ -22700,31 +22700,25 @@
         </is>
       </c>
       <c r="I2" s="37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="37" t="inlineStr">
         <is>
-          <t>Assured peak supply</t>
+          <t>Standalone BESS under VGF and TBCB</t>
         </is>
       </c>
       <c r="K2" s="274" t="n"/>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="L2" s="37" t="n"/>
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>As per RfS</t>
         </is>
       </c>
-      <c r="M2" s="37" t="inlineStr">
-        <is>
-          <t>As per RfS</t>
-        </is>
-      </c>
       <c r="N2" s="280" t="n">
-        <v>46241.75</v>
+        <v>46255</v>
       </c>
       <c r="O2" s="280" t="n"/>
-      <c r="P2" s="280" t="n">
-        <v>46246.41666666666</v>
-      </c>
+      <c r="P2" s="280" t="n"/>
       <c r="Q2" s="280" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22734,17 +22728,17 @@
         <v>46236</v>
       </c>
       <c r="S2" s="37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T2" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tender-details/Ymd_</t>
+          <t>https://sjvn.nic.in/en/tender</t>
         </is>
       </c>
       <c r="U2" s="37" t="n"/>
       <c r="V2" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
+          <t>265 MW / 530 MWh BESS in Haryana</t>
         </is>
       </c>
       <c r="W2" s="278">
@@ -22764,7 +22758,7 @@
         <v/>
       </c>
       <c r="AA2">
-        <f>IF(A3="","",C3&amp;"|"&amp;E3&amp;"|"&amp;TEXT(N3,"yyyymmdd")&amp;"|"&amp;Q3&amp;"|"&amp;S3&amp;"|"&amp;TEXT(AI3,"yyyymmdd"))</f>
+        <f>IF(A4="","",C4&amp;"|"&amp;E4&amp;"|"&amp;TEXT(N4,"yyyymmdd")&amp;"|"&amp;Q4&amp;"|"&amp;S4&amp;"|"&amp;TEXT(AI4,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB2" s="281" t="n">
@@ -22781,129 +22775,116 @@
         </is>
       </c>
       <c r="AE2" s="281">
-        <f>IF(A3="","",IF(AC3="Official agency page",3,IF(AC3="Official government portal",3,IF(AC3="Official tender document",4,1)))+IF(AD3="Core fields",2,1))</f>
+        <f>IF(A4="","",IF(AC4="Official agency page",3,IF(AC4="Official government portal",3,IF(AC4="Official tender document",4,1)))+IF(AD4="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF2" s="281">
-        <f>IF(A3="","",IF(OR(Q3="Open",Q3="Extended"),"Current Opportunity",IF(Q3="Corrigendum","Needs Status Check",IF(Q3="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A4="","",IF(OR(Q4="Open",Q4="Extended"),"Current Opportunity",IF(Q4="Corrigendum","Needs Status Check",IF(Q4="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG2" s="281" t="n">
-        <v>46178</v>
-      </c>
-      <c r="AH2" s="281" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ; -; 0; 2; 6; 7; 8; ;</t>
-        </is>
-      </c>
-      <c r="AI2" s="281" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
+        <v>46227</v>
+      </c>
+      <c r="AH2" s="281" t="n"/>
+      <c r="AI2" s="281" t="n"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Amendment-01 uploaded 08-Jul-2026</t>
+          <t>No corrigendum identified in the captured official listing.</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Tariff-based competitive bidding with PPA/PSA</t>
+          <t>Standalone BESS under VGF and tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Buying Entity selects 4 hours daily across evening-to-next-morning non-solar peak hours; at least one continuous hour</t>
+          <t>Dispatch schedule and availability obligations governed by RfS/BESSA/BESPA</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4 MWh per MW contracted capacity per day; for 1,200 MW = 4,800 MWh/day</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Monthly reconciliation. Minimum effective supply = 90% of monthly scheduled peak-energy requirement before penalty applies</t>
+          <t>PLF is not applicable to standalone BESS; monthly availability/energy obligations require document review</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>100% annual offered energy must be renewable. No annual PLF/CUF percentage stated</t>
+          <t>Annual PLF/CUF not applicable; annual availability/cycle obligations require document review</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Monthly shortfall up to 10% below required peak energy permitted</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Shortfall beyond 10% monthly: 1.5 × PPA tariff × energy shortfall</t>
+          <t>Not verified from accessible document text</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Yes — green-market sources or bilateral RE agreements permitted</t>
+          <t>Charging-source provision not verified from accessible document text</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Up to 5% of total annual required energy</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>External RE may directly meet peak requirements or charge ESS. Only discharged ESS energy counts toward the 5%; excess above 5% is unpaid and excluded from performance</t>
+          <t>Official RfS PDF was listed but could not be reliably fetched in this review</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>ESS may be used outside peak hours for third-party/exchange sale after PPA obligations. Sale before fulfilling obligations attracts 1.5 × highest DAM/GDAM/RTM market rate per kWh, in addition to shortfall penalty</t>
+          <t>Merchant-use rights not verified</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/uploads/tenders/RfS_for_4800_MWh_Peak_Supply_%28FDRE-IX%29-_final_upload.pdf</t>
+          <t>https://sjvn.nic.in/sites/default/files/2026-07/RfS%20BESS%202%20240726.pdf</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Verified from official RfS; latest SECI page shows revised bid dates</t>
+          <t>Document-level review pending; no assumptions inserted</t>
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46241.20385158412</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
-        </is>
+        <v>46242.17140645588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>SJVN-BESS2</t>
+          <t>MSEDCL-BESS-2000</t>
         </is>
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="C3" s="37" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>MSEDCL</t>
         </is>
       </c>
       <c r="D3" s="37" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E3" s="37" t="inlineStr">
         <is>
-          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
+          <t>RfS-2000MW-4000MWh-BESS-2026</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
@@ -22912,7 +22893,7 @@
         </is>
       </c>
       <c r="G3" s="274" t="n">
-        <v>265</v>
+        <v>2000</v>
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
@@ -22924,7 +22905,7 @@
       </c>
       <c r="J3" s="37" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and TBCB</t>
+          <t>Tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="K3" s="274" t="n"/>
@@ -22934,31 +22915,29 @@
           <t>As per RfS</t>
         </is>
       </c>
-      <c r="N3" s="280" t="n">
-        <v>46255</v>
-      </c>
+      <c r="N3" s="280" t="n"/>
       <c r="O3" s="280" t="n"/>
       <c r="P3" s="280" t="n"/>
       <c r="Q3" s="280" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Corrigendum</t>
         </is>
       </c>
       <c r="R3" s="280" t="n">
         <v>46236</v>
       </c>
       <c r="S3" s="37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" s="37" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/en/tender</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="U3" s="37" t="n"/>
       <c r="V3" s="37" t="inlineStr">
         <is>
-          <t>265 MW / 530 MWh BESS in Haryana</t>
+          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
         </is>
       </c>
       <c r="W3" s="278">
@@ -22978,7 +22957,7 @@
         <v/>
       </c>
       <c r="AA3">
-        <f>IF(A4="","",C4&amp;"|"&amp;E4&amp;"|"&amp;TEXT(N4,"yyyymmdd")&amp;"|"&amp;Q4&amp;"|"&amp;S4&amp;"|"&amp;TEXT(AI4,"yyyymmdd"))</f>
+        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB3" s="281" t="n">
@@ -22991,65 +22970,71 @@
       </c>
       <c r="AD3" s="281" t="inlineStr">
         <is>
-          <t>Core fields</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="AE3" s="281">
-        <f>IF(A4="","",IF(AC4="Official agency page",3,IF(AC4="Official government portal",3,IF(AC4="Official tender document",4,1)))+IF(AD4="Core fields",2,1))</f>
+        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF3" s="281">
-        <f>IF(A4="","",IF(OR(Q4="Open",Q4="Extended"),"Current Opportunity",IF(Q4="Corrigendum","Needs Status Check",IF(Q4="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG3" s="281" t="n">
-        <v>46227</v>
-      </c>
-      <c r="AH3" s="281" t="n"/>
-      <c r="AI3" s="281" t="n"/>
+        <v>46203</v>
+      </c>
+      <c r="AH3" s="281" t="inlineStr">
+        <is>
+          <t>2026-07-07; 2026-07-22</t>
+        </is>
+      </c>
+      <c r="AI3" s="281" t="n">
+        <v>46225</v>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>No corrigendum identified in the captured official listing.</t>
+          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and tariff-based competitive bidding</t>
+          <t>Standalone BESS under tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Dispatch schedule and availability obligations governed by RfS/BESSA/BESPA</t>
+          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>PLF is not applicable to standalone BESS; monthly availability/energy obligations require document review</t>
+          <t>Monthly availability/payment condition not verified from accessible current document text</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Annual PLF/CUF not applicable; annual availability/cycle obligations require document review</t>
+          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Charging-source provision not verified from accessible document text</t>
+          <t>Charging source and grid/exchange charging permission not verified</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -23059,7 +23044,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>Official RfS PDF was listed but could not be reliably fetched in this review</t>
+          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -23069,95 +23054,81 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/sites/default/files/2026-07/RfS%20BESS%202%20240726.pdf</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Document-level review pending; no assumptions inserted</t>
+          <t>Tender confirmed; commercial clause extraction pending</t>
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL-BESS-2000</t>
+          <t>SECI000240</t>
         </is>
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>Maharashtra</t>
-        </is>
-      </c>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="n"/>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>RfS-2000MW-4000MWh-BESS-2026</t>
+          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>FDRE</t>
         </is>
       </c>
       <c r="G4" s="274" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="37" t="inlineStr">
-        <is>
-          <t>Tariff-based competitive bidding</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="n"/>
+      <c r="J4" s="37" t="n"/>
       <c r="K4" s="274" t="n"/>
       <c r="L4" s="37" t="n"/>
-      <c r="M4" s="37" t="inlineStr">
-        <is>
-          <t>As per RfS</t>
-        </is>
-      </c>
+      <c r="M4" s="37" t="n"/>
       <c r="N4" s="280" t="n"/>
       <c r="O4" s="280" t="n"/>
       <c r="P4" s="280" t="n"/>
       <c r="Q4" s="280" t="inlineStr">
         <is>
-          <t>Corrigendum</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="R4" s="280" t="n">
-        <v>46236</v>
+        <v>46237.26024921297</v>
       </c>
       <c r="S4" s="37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4" s="37" t="inlineStr">
         <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
+          <t>https://www.seci.co.in/tender-details/YmZ3</t>
         </is>
       </c>
       <c r="U4" s="37" t="n"/>
       <c r="V4" s="37" t="inlineStr">
         <is>
-          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
+          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
         </is>
       </c>
       <c r="W4" s="278">
@@ -23176,122 +23147,32 @@
         <f>IF(Y4="","",IF(COUNTIF($Y$2:$Y$501,Y4)&gt;1,"Duplicate","Unique"))</f>
         <v/>
       </c>
-      <c r="AA4">
-        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="281" t="n">
-        <v>46236</v>
-      </c>
+      <c r="AB4" s="281" t="n"/>
       <c r="AC4" s="281" t="inlineStr">
         <is>
           <t>Official agency page</t>
         </is>
       </c>
-      <c r="AD4" s="281" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="AE4" s="281">
-        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="281">
-        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="281" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AH4" s="281" t="inlineStr">
-        <is>
-          <t>2026-07-07; 2026-07-22</t>
-        </is>
-      </c>
-      <c r="AI4" s="281" t="n">
-        <v>46225</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Standalone BESS under tariff-based competitive bidding</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Monthly availability/payment condition not verified from accessible current document text</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>Charging source and grid/exchange charging permission not verified</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Merchant-use rights not verified</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Tender confirmed; commercial clause extraction pending</t>
-        </is>
+      <c r="AD4" s="281" t="n"/>
+      <c r="AE4" s="281" t="n"/>
+      <c r="AF4" s="281" t="n"/>
+      <c r="AG4" s="281" t="n"/>
+      <c r="AH4" s="281" t="n"/>
+      <c r="AI4" s="281" t="n"/>
+      <c r="AX4" s="282" t="n">
+        <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>SECI000240</t>
-        </is>
-      </c>
+      <c r="A5" s="37" t="n"/>
       <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Central</t>
@@ -23299,22 +23180,18 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>SECI</t>
+          <t>NTPC REL</t>
         </is>
       </c>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
-        </is>
-      </c>
+      <c r="E5" s="37" t="inlineStr"/>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>FDRE</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G5" s="274" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
@@ -23335,20 +23212,18 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46237.26024921297</v>
-      </c>
-      <c r="S5" s="37" t="n">
-        <v>0</v>
-      </c>
+        <v>46242.17140645588</v>
+      </c>
+      <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tender-details/YmZ3</t>
-        </is>
-      </c>
-      <c r="U5" s="37" t="n"/>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
+        </is>
+      </c>
+      <c r="U5" s="37" t="inlineStr"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
+          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
         </is>
       </c>
       <c r="W5" s="278">
@@ -23380,14 +23255,14 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46237.26024921297</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
         </is>
       </c>
     </row>
@@ -23395,23 +23270,27 @@
       <c r="A6" s="37" t="n"/>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>NTPC REL</t>
+          <t>GRIDCO</t>
         </is>
       </c>
       <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="inlineStr"/>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
+        </is>
+      </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="G6" s="274" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
@@ -23432,18 +23311,18 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
         <is>
-          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
+          <t>https://www.gridco.co.in/tender.aspx</t>
         </is>
       </c>
       <c r="U6" s="37" t="inlineStr"/>
       <c r="V6" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
+          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23475,14 +23354,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
+          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
         </is>
       </c>
     </row>
@@ -23501,7 +23380,7 @@
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
+          <t>Scope of Work :</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
@@ -23531,7 +23410,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23542,7 +23421,7 @@
       <c r="U7" s="37" t="inlineStr"/>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W7" s="278">
@@ -23574,48 +23453,26 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
+          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n"/>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>Odisha</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>GRIDCO</t>
-        </is>
-      </c>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
       <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>Scope of Work :</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="G8" s="274" t="n">
-        <v>225</v>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="274" t="n"/>
+      <c r="H8" s="37" t="n"/>
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="274" t="n"/>
@@ -23624,65 +23481,23 @@
       <c r="N8" s="280" t="n"/>
       <c r="O8" s="280" t="n"/>
       <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R8" s="280" t="n">
-        <v>46241.20385158412</v>
-      </c>
+      <c r="Q8" s="280" t="n"/>
+      <c r="R8" s="280" t="n"/>
       <c r="S8" s="37" t="n"/>
-      <c r="T8" s="37" t="inlineStr">
-        <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
-        </is>
-      </c>
-      <c r="U8" s="37" t="inlineStr"/>
-      <c r="V8" s="37" t="inlineStr">
-        <is>
-          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
-        </is>
-      </c>
-      <c r="W8" s="278">
-        <f>IF(N8="","",N8-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>IF(W8="","",IF(W8&lt;0,"Expired",IF(W8&lt;=3,"Urgent",IF(W8&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>UPPER(TRIM(C8&amp;"|"&amp;E8))</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>IF(Y8="","",IF(COUNTIF($Y$2:$Y$501,Y8)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="T8" s="37" t="n"/>
+      <c r="U8" s="37" t="n"/>
+      <c r="V8" s="37" t="n"/>
+      <c r="W8" s="278" t="n"/>
       <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC8" s="281" t="n"/>
       <c r="AD8" s="281" t="n"/>
       <c r="AE8" s="281" t="n"/>
       <c r="AF8" s="281" t="n"/>
       <c r="AG8" s="281" t="n"/>
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
-      <c r="AX8" s="282" t="n">
-        <v>46241.20385158412</v>
-      </c>
-      <c r="AY8" s="282" t="n">
-        <v>46241.20385158412</v>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
-        </is>
-      </c>
+      <c r="AX8" s="282" t="n"/>
+      <c r="AY8" s="282" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n"/>
@@ -43560,7 +43375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -46060,13 +45875,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -46092,7 +45905,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46125,7 +45937,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46154,6 +45965,452 @@
       <c r="H72" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>88</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>40</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>25</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>813</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29985</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SECI000258</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>FDRE</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Deadline expired without verified extension</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd_</t>
         </is>
       </c>
     </row>
@@ -48596,7 +48853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -48812,7 +49069,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46242.17140645588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -50902,15 +51159,36 @@
         </is>
       </c>
       <c r="G509" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46241.20385158565</v>
       </c>
       <c r="H509" s="282" t="n">
-        <v>46241.20385158412</v>
+        <v>46241.20385158565</v>
       </c>
       <c r="I509" t="n">
         <v>7</v>
       </c>
       <c r="J509" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>RUN-20260808040649</t>
+        </is>
+      </c>
+      <c r="G510" s="282" t="n">
+        <v>46242.17140645588</v>
+      </c>
+      <c r="H510" s="282" t="n">
+        <v>46242.17140645588</v>
+      </c>
+      <c r="I510" t="n">
+        <v>6</v>
+      </c>
+      <c r="J510" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23172,7 +23172,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="n"/>
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>SECI000258</t>
+        </is>
+      </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Central</t>
@@ -23180,25 +23184,31 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>NTPC REL</t>
+          <t>SECI</t>
         </is>
       </c>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="37" t="inlineStr"/>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
+        </is>
+      </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>FDRE</t>
         </is>
       </c>
       <c r="G5" s="274" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>4</v>
+      </c>
       <c r="J5" s="37" t="n"/>
       <c r="K5" s="274" t="n"/>
       <c r="L5" s="37" t="n"/>
@@ -23212,18 +23222,18 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
+          <t>https://www.seci.co.in/tender-details/Ymd_</t>
         </is>
       </c>
       <c r="U5" s="37" t="inlineStr"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
+          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
         </is>
       </c>
       <c r="W5" s="278">
@@ -23255,14 +23265,14 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
+          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
         </is>
       </c>
     </row>
@@ -23270,27 +23280,23 @@
       <c r="A6" s="37" t="n"/>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>GRIDCO</t>
+          <t>NTPC REL</t>
         </is>
       </c>
       <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
-        </is>
-      </c>
+      <c r="E6" s="37" t="inlineStr"/>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G6" s="274" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
@@ -23311,18 +23317,18 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
         <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
         </is>
       </c>
       <c r="U6" s="37" t="inlineStr"/>
       <c r="V6" s="37" t="inlineStr">
         <is>
-          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23354,14 +23360,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
+          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23386,7 @@
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>Scope of Work :</t>
+          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
@@ -23410,7 +23416,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23421,7 +23427,7 @@
       <c r="U7" s="37" t="inlineStr"/>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
         </is>
       </c>
       <c r="W7" s="278">
@@ -23453,26 +23459,48 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
+          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n"/>
-      <c r="B8" s="37" t="n"/>
-      <c r="C8" s="37" t="n"/>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
       <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="274" t="n"/>
-      <c r="H8" s="37" t="n"/>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Scope of Work :</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="G8" s="274" t="n">
+        <v>225</v>
+      </c>
+      <c r="H8" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="274" t="n"/>
@@ -23481,23 +23509,65 @@
       <c r="N8" s="280" t="n"/>
       <c r="O8" s="280" t="n"/>
       <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="n"/>
-      <c r="R8" s="280" t="n"/>
+      <c r="Q8" s="280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R8" s="280" t="n">
+        <v>46243.17686518606</v>
+      </c>
       <c r="S8" s="37" t="n"/>
-      <c r="T8" s="37" t="n"/>
-      <c r="U8" s="37" t="n"/>
-      <c r="V8" s="37" t="n"/>
-      <c r="W8" s="278" t="n"/>
+      <c r="T8" s="37" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/tender.aspx</t>
+        </is>
+      </c>
+      <c r="U8" s="37" t="inlineStr"/>
+      <c r="V8" s="37" t="inlineStr">
+        <is>
+          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
+        </is>
+      </c>
+      <c r="W8" s="278">
+        <f>IF(N8="","",N8-TODAY())</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>IF(W8="","",IF(W8&lt;0,"Expired",IF(W8&lt;=3,"Urgent",IF(W8&lt;=7,"Due in 7 Days","Normal"))))</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>UPPER(TRIM(C8&amp;"|"&amp;E8))</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>IF(Y8="","",IF(COUNTIF($Y$2:$Y$501,Y8)&gt;1,"Duplicate","Unique"))</f>
+        <v/>
+      </c>
       <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="n"/>
+      <c r="AC8" s="281" t="inlineStr">
+        <is>
+          <t>Official agency page</t>
+        </is>
+      </c>
       <c r="AD8" s="281" t="n"/>
       <c r="AE8" s="281" t="n"/>
       <c r="AF8" s="281" t="n"/>
       <c r="AG8" s="281" t="n"/>
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
-      <c r="AX8" s="282" t="n"/>
-      <c r="AY8" s="282" t="n"/>
+      <c r="AX8" s="282" t="n">
+        <v>46243.17686518606</v>
+      </c>
+      <c r="AY8" s="282" t="n">
+        <v>46243.17686518606</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n"/>
@@ -43375,7 +43445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -46277,13 +46347,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -46309,7 +46377,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46342,7 +46409,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46411,6 +46477,412 @@
       <c r="H84" t="inlineStr">
         <is>
           <t>https://www.seci.co.in/tender-details/Ymd_</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>88</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>40</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>813</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29985</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
       </c>
     </row>
@@ -48853,7 +49325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J510"/>
+  <dimension ref="A1:J511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -49069,7 +49541,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46243.17686518606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -51180,15 +51652,36 @@
         </is>
       </c>
       <c r="G510" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46242.17140645834</v>
       </c>
       <c r="H510" s="282" t="n">
-        <v>46242.17140645588</v>
+        <v>46242.17140645834</v>
       </c>
       <c r="I510" t="n">
         <v>6</v>
       </c>
       <c r="J510" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>RUN-20260809041441</t>
+        </is>
+      </c>
+      <c r="G511" s="282" t="n">
+        <v>46243.17686518606</v>
+      </c>
+      <c r="H511" s="282" t="n">
+        <v>46243.17686518606</v>
+      </c>
+      <c r="I511" t="n">
+        <v>7</v>
+      </c>
+      <c r="J511" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23222,15 +23222,17 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46243.17686518606</v>
-      </c>
-      <c r="S5" s="37" t="n"/>
+        <v>46243.17686518518</v>
+      </c>
+      <c r="S5" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" s="37" t="inlineStr">
         <is>
           <t>https://www.seci.co.in/tender-details/Ymd_</t>
         </is>
       </c>
-      <c r="U5" s="37" t="inlineStr"/>
+      <c r="U5" s="37" t="n"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
@@ -23262,13 +23264,13 @@
       <c r="AE5" s="281" t="n"/>
       <c r="AF5" s="281" t="n"/>
       <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
+      <c r="AH5" s="281" t="inlineStr"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23317,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23360,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -23416,7 +23418,7 @@
         </is>
       </c>
       <c r="R7" s="280" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="S7" s="37" t="n"/>
       <c r="T7" s="37" t="inlineStr">
@@ -23459,10 +23461,10 @@
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
       <c r="AX7" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AY7" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -23515,7 +23517,7 @@
         </is>
       </c>
       <c r="R8" s="280" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="S8" s="37" t="n"/>
       <c r="T8" s="37" t="inlineStr">
@@ -23558,10 +23560,10 @@
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
       <c r="AX8" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AY8" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -43445,7 +43447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -46789,13 +46791,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -46821,7 +46821,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46854,7 +46853,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -46881,6 +46879,412 @@
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>88</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>40</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>25</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>813</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/29985</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -49325,7 +49729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J511"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -49541,7 +49945,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46244.18863748031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -51673,15 +52077,36 @@
         </is>
       </c>
       <c r="G511" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46243.17686518518</v>
       </c>
       <c r="H511" s="282" t="n">
-        <v>46243.17686518606</v>
+        <v>46243.17686518518</v>
       </c>
       <c r="I511" t="n">
         <v>7</v>
       </c>
       <c r="J511" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>RUN-20260810043138</t>
+        </is>
+      </c>
+      <c r="G512" s="282" t="n">
+        <v>46244.18863748031</v>
+      </c>
+      <c r="H512" s="282" t="n">
+        <v>46244.18863748031</v>
+      </c>
+      <c r="I512" t="n">
+        <v>7</v>
+      </c>
+      <c r="J512" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23362,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -23375,35 +23375,13 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="n"/>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>Odisha</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>GRIDCO</t>
-        </is>
-      </c>
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
       <c r="D7" s="37" t="n"/>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental </t>
-        </is>
-      </c>
-      <c r="F7" s="37" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="G7" s="274" t="n">
-        <v>225</v>
-      </c>
-      <c r="H7" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="274" t="n"/>
+      <c r="H7" s="37" t="n"/>
       <c r="I7" s="37" t="n"/>
       <c r="J7" s="37" t="n"/>
       <c r="K7" s="274" t="n"/>
@@ -23412,97 +23390,33 @@
       <c r="N7" s="280" t="n"/>
       <c r="O7" s="280" t="n"/>
       <c r="P7" s="280" t="n"/>
-      <c r="Q7" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R7" s="280" t="n">
-        <v>46244.18863748031</v>
-      </c>
+      <c r="Q7" s="280" t="n"/>
+      <c r="R7" s="280" t="n"/>
       <c r="S7" s="37" t="n"/>
-      <c r="T7" s="37" t="inlineStr">
-        <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
-        </is>
-      </c>
-      <c r="U7" s="37" t="inlineStr"/>
-      <c r="V7" s="37" t="inlineStr">
-        <is>
-          <t>Issuing Authority : | GRIDCO Ltd. | Date of Opening : | 08/10/2026 05:00 PM | Scope of Work : | Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Issuing Authority : GRIDCO Ltd. Date of Opening : 08/10/2026 05:00 PM Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
-        </is>
-      </c>
-      <c r="W7" s="278">
-        <f>IF(N7="","",N7-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>IF(W7="","",IF(W7&lt;0,"Expired",IF(W7&lt;=3,"Urgent",IF(W7&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>UPPER(TRIM(C7&amp;"|"&amp;E7))</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>IF(Y7="","",IF(COUNTIF($Y$2:$Y$501,Y7)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="T7" s="37" t="n"/>
+      <c r="U7" s="37" t="n"/>
+      <c r="V7" s="37" t="n"/>
+      <c r="W7" s="278" t="n"/>
       <c r="AB7" s="281" t="n"/>
-      <c r="AC7" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC7" s="281" t="n"/>
       <c r="AD7" s="281" t="n"/>
       <c r="AE7" s="281" t="n"/>
       <c r="AF7" s="281" t="n"/>
       <c r="AG7" s="281" t="n"/>
       <c r="AH7" s="281" t="n"/>
       <c r="AI7" s="281" t="n"/>
-      <c r="AX7" s="282" t="n">
-        <v>46244.18863748031</v>
-      </c>
-      <c r="AY7" s="282" t="n">
-        <v>46244.18863748031</v>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>b2f0cf79f5c1c721a8ebf084bb1191b1315d06687fed6cfce2722ac666e4b587</t>
-        </is>
-      </c>
+      <c r="AX7" s="282" t="n"/>
+      <c r="AY7" s="282" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n"/>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>Odisha</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>GRIDCO</t>
-        </is>
-      </c>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
       <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>Scope of Work :</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="G8" s="274" t="n">
-        <v>225</v>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="274" t="n"/>
+      <c r="H8" s="37" t="n"/>
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="274" t="n"/>
@@ -23511,65 +23425,23 @@
       <c r="N8" s="280" t="n"/>
       <c r="O8" s="280" t="n"/>
       <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R8" s="280" t="n">
-        <v>46244.18863748031</v>
-      </c>
+      <c r="Q8" s="280" t="n"/>
+      <c r="R8" s="280" t="n"/>
       <c r="S8" s="37" t="n"/>
-      <c r="T8" s="37" t="inlineStr">
-        <is>
-          <t>https://www.gridco.co.in/tender.aspx</t>
-        </is>
-      </c>
-      <c r="U8" s="37" t="inlineStr"/>
-      <c r="V8" s="37" t="inlineStr">
-        <is>
-          <t>Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India. Scope of Work : Request for Proposal for consultancy services for Environmental and Social Impact Assessment (ESIA) for 225 MW Upper Indravati Floating Solar Project including evacuation infrastructure and associated transmission lines in the state of Odisha, India.</t>
-        </is>
-      </c>
-      <c r="W8" s="278">
-        <f>IF(N8="","",N8-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>IF(W8="","",IF(W8&lt;0,"Expired",IF(W8&lt;=3,"Urgent",IF(W8&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>UPPER(TRIM(C8&amp;"|"&amp;E8))</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>IF(Y8="","",IF(COUNTIF($Y$2:$Y$501,Y8)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="T8" s="37" t="n"/>
+      <c r="U8" s="37" t="n"/>
+      <c r="V8" s="37" t="n"/>
+      <c r="W8" s="278" t="n"/>
       <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC8" s="281" t="n"/>
       <c r="AD8" s="281" t="n"/>
       <c r="AE8" s="281" t="n"/>
       <c r="AF8" s="281" t="n"/>
       <c r="AG8" s="281" t="n"/>
       <c r="AH8" s="281" t="n"/>
       <c r="AI8" s="281" t="n"/>
-      <c r="AX8" s="282" t="n">
-        <v>46244.18863748031</v>
-      </c>
-      <c r="AY8" s="282" t="n">
-        <v>46244.18863748031</v>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>825330359c0f821ed1c3004804005ec76fb9242a1c591679df676bf7d493ffea</t>
-        </is>
-      </c>
+      <c r="AX8" s="282" t="n"/>
+      <c r="AY8" s="282" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n"/>
@@ -43447,7 +43319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -47193,13 +47065,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -47225,7 +47095,6 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47258,7 +47127,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47285,6 +47153,380 @@
         </is>
       </c>
       <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>88</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>40</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>25</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -49729,7 +49971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J512"/>
+  <dimension ref="A1:J513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -49945,7 +50187,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46245.17875561945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -52098,15 +52340,36 @@
         </is>
       </c>
       <c r="G512" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46244.18863747685</v>
       </c>
       <c r="H512" s="282" t="n">
-        <v>46244.18863748031</v>
+        <v>46244.18863747685</v>
       </c>
       <c r="I512" t="n">
         <v>7</v>
       </c>
       <c r="J512" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>RUN-20260811041724</t>
+        </is>
+      </c>
+      <c r="G513" s="282" t="n">
+        <v>46245.17875561945</v>
+      </c>
+      <c r="H513" s="282" t="n">
+        <v>46245.17875561945</v>
+      </c>
+      <c r="I513" t="n">
+        <v>5</v>
+      </c>
+      <c r="J513" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23362,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -47467,7 +47467,6 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47500,7 +47499,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47527,6 +47525,380 @@
         </is>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>88</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>40</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>25</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -49971,7 +50343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -50187,7 +50559,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46246.19384329564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -52361,15 +52733,36 @@
         </is>
       </c>
       <c r="G513" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46245.178755625</v>
       </c>
       <c r="H513" s="282" t="n">
-        <v>46245.17875561945</v>
+        <v>46245.178755625</v>
       </c>
       <c r="I513" t="n">
         <v>5</v>
       </c>
       <c r="J513" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>RUN-20260812043908</t>
+        </is>
+      </c>
+      <c r="G514" s="282" t="n">
+        <v>46246.19384329564</v>
+      </c>
+      <c r="H514" s="282" t="n">
+        <v>46246.19384329564</v>
+      </c>
+      <c r="I514" t="n">
+        <v>5</v>
+      </c>
+      <c r="J514" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23362,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -47839,7 +47839,6 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47872,7 +47871,6 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -47899,6 +47897,380 @@
         </is>
       </c>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>88</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>40</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -50343,7 +50715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J514"/>
+  <dimension ref="A1:J515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -50559,7 +50931,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46247.19564244521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -52754,15 +53126,36 @@
         </is>
       </c>
       <c r="G514" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46246.19384329861</v>
       </c>
       <c r="H514" s="282" t="n">
-        <v>46246.19384329564</v>
+        <v>46246.19384329861</v>
       </c>
       <c r="I514" t="n">
         <v>5</v>
       </c>
       <c r="J514" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>RUN-20260813044143</t>
+        </is>
+      </c>
+      <c r="G515" s="282" t="n">
+        <v>46247.19564244521</v>
+      </c>
+      <c r="H515" s="282" t="n">
+        <v>46247.19564244521</v>
+      </c>
+      <c r="I515" t="n">
+        <v>5</v>
+      </c>
+      <c r="J515" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23362,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -48211,7 +48211,6 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -48244,7 +48243,6 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -48271,6 +48269,380 @@
         </is>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>88</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>40</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>25</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -50715,7 +51087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J515"/>
+  <dimension ref="A1:J516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -50931,7 +51303,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46248.19364602502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -53147,15 +53519,36 @@
         </is>
       </c>
       <c r="G515" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46247.19564244213</v>
       </c>
       <c r="H515" s="282" t="n">
-        <v>46247.19564244521</v>
+        <v>46247.19564244213</v>
       </c>
       <c r="I515" t="n">
         <v>5</v>
       </c>
       <c r="J515" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>RUN-20260814043851</t>
+        </is>
+      </c>
+      <c r="G516" s="282" t="n">
+        <v>46248.19364602502</v>
+      </c>
+      <c r="H516" s="282" t="n">
+        <v>46248.19364602502</v>
+      </c>
+      <c r="I516" t="n">
+        <v>5</v>
+      </c>
+      <c r="J516" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23362,10 +23362,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -48583,7 +48583,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -48616,7 +48615,6 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -48643,6 +48641,413 @@
         </is>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>88</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>40</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>25</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -51087,7 +51492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J516"/>
+  <dimension ref="A1:J517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -51303,7 +51708,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46249.14518179359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -53540,15 +53945,36 @@
         </is>
       </c>
       <c r="G516" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46248.19364603009</v>
       </c>
       <c r="H516" s="282" t="n">
-        <v>46248.19364602502</v>
+        <v>46248.19364603009</v>
       </c>
       <c r="I516" t="n">
         <v>5</v>
       </c>
       <c r="J516" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>RUN-20260815032903</t>
+        </is>
+      </c>
+      <c r="G517" s="282" t="n">
+        <v>46249.14518179359</v>
+      </c>
+      <c r="H517" s="282" t="n">
+        <v>46249.14518179359</v>
+      </c>
+      <c r="I517" t="n">
+        <v>5</v>
+      </c>
+      <c r="J517" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46250.15539132704</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46250.15539132704</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46250.15539132704</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46250.15539132704</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23280,31 +23280,13 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="n"/>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>NTPC REL</t>
-        </is>
-      </c>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
       <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="inlineStr"/>
-      <c r="F6" s="37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G6" s="274" t="n">
-        <v>300</v>
-      </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="274" t="n"/>
+      <c r="H6" s="37" t="n"/>
       <c r="I6" s="37" t="n"/>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="274" t="n"/>
@@ -23313,65 +23295,23 @@
       <c r="N6" s="280" t="n"/>
       <c r="O6" s="280" t="n"/>
       <c r="P6" s="280" t="n"/>
-      <c r="Q6" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R6" s="280" t="n">
-        <v>46249.14518179359</v>
-      </c>
+      <c r="Q6" s="280" t="n"/>
+      <c r="R6" s="280" t="n"/>
       <c r="S6" s="37" t="n"/>
-      <c r="T6" s="37" t="inlineStr">
-        <is>
-          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30126</t>
-        </is>
-      </c>
-      <c r="U6" s="37" t="inlineStr"/>
-      <c r="V6" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  | GEM/2026/B/7880246 |  | Hiring of 01 No. 4 - Wheel drive Vehicle for Block-VI (300MW) PV Project for 02 Years | Renewable Energy | 17/08/2026 | </t>
-        </is>
-      </c>
-      <c r="W6" s="278">
-        <f>IF(N6="","",N6-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>IF(W6="","",IF(W6&lt;0,"Expired",IF(W6&lt;=3,"Urgent",IF(W6&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>UPPER(TRIM(C6&amp;"|"&amp;E6))</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>IF(Y6="","",IF(COUNTIF($Y$2:$Y$501,Y6)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="T6" s="37" t="n"/>
+      <c r="U6" s="37" t="n"/>
+      <c r="V6" s="37" t="n"/>
+      <c r="W6" s="278" t="n"/>
       <c r="AB6" s="281" t="n"/>
-      <c r="AC6" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC6" s="281" t="n"/>
       <c r="AD6" s="281" t="n"/>
       <c r="AE6" s="281" t="n"/>
       <c r="AF6" s="281" t="n"/>
       <c r="AG6" s="281" t="n"/>
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
-      <c r="AX6" s="282" t="n">
-        <v>46249.14518179359</v>
-      </c>
-      <c r="AY6" s="282" t="n">
-        <v>46249.14518179359</v>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>ebc65659fff7297cab0cec874c9a8bfb85290b5489c5eb69ed4fa17fa13c8dca</t>
-        </is>
-      </c>
+      <c r="AX6" s="282" t="n"/>
+      <c r="AY6" s="282" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="37" t="n"/>
@@ -43319,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -48955,7 +48895,6 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -48988,7 +48927,6 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49021,7 +48959,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49048,6 +48985,512 @@
         </is>
       </c>
       <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>88</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>40</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>25</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>MPUVNL</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tenders</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://mptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=Home&amp;service=direct&amp;session=T&amp;sp=SXQfAfEZ1orhTC5Yzc7r5bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>MPUVNL</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>1. Construction of 3.50 meter wide RCC Nalla including covering with RCC Slab behind Bhojpur Club, E-1, Arera Colony, Bhopal 56/SAC dt. 07.08.2026 21-</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://mptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=Home&amp;service=direct&amp;session=T&amp;sp=SXQfAfEZ1orhTC5Yzc7r5bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>MPUVNL</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10. Maintenance and various reparing work, under ground water storage tank etc. work in VVIP Residential bungalow under HQ section of HQ 3 sub divisio</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://mptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=Home&amp;service=direct&amp;session=T&amp;sp=Std%2BXGPFig0FPEcyX5KFg9Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -51492,7 +51935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J517"/>
+  <dimension ref="A1:J518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -51708,7 +52151,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46250.15539132704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -53966,15 +54409,36 @@
         </is>
       </c>
       <c r="G517" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46249.14518179398</v>
       </c>
       <c r="H517" s="282" t="n">
-        <v>46249.14518179359</v>
+        <v>46249.14518179398</v>
       </c>
       <c r="I517" t="n">
         <v>5</v>
       </c>
       <c r="J517" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>RUN-20260816034345</t>
+        </is>
+      </c>
+      <c r="G518" s="282" t="n">
+        <v>46250.15539132704</v>
+      </c>
+      <c r="H518" s="282" t="n">
+        <v>46250.15539132704</v>
+      </c>
+      <c r="I518" t="n">
+        <v>4</v>
+      </c>
+      <c r="J518" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46251.15609919124</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46251.15609919124</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46251.15609919124</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46251.15609919124</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -49299,7 +49299,6 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -49332,7 +49331,6 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>MPUVNL</t>
@@ -49365,7 +49363,6 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>MPUVNL</t>
@@ -49398,7 +49395,6 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>MPUVNL</t>
@@ -49431,7 +49427,6 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49464,7 +49459,6 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49491,6 +49485,413 @@
         </is>
       </c>
       <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>88</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>40</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>25</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -51935,7 +52336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J518"/>
+  <dimension ref="A1:J519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -52151,7 +52552,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46251.15609919124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -54430,15 +54831,36 @@
         </is>
       </c>
       <c r="G518" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46250.15539133102</v>
       </c>
       <c r="H518" s="282" t="n">
-        <v>46250.15539132704</v>
+        <v>46250.15539133102</v>
       </c>
       <c r="I518" t="n">
         <v>4</v>
       </c>
       <c r="J518" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>RUN-20260817034446</t>
+        </is>
+      </c>
+      <c r="G519" s="282" t="n">
+        <v>46251.15609919124</v>
+      </c>
+      <c r="H519" s="282" t="n">
+        <v>46251.15609919124</v>
+      </c>
+      <c r="I519" t="n">
+        <v>4</v>
+      </c>
+      <c r="J519" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46252.15456611976</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46252.15456611976</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46252.15456611976</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46252.15456611976</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -49799,7 +49799,6 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -49832,7 +49831,6 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49865,7 +49863,6 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -49892,6 +49889,413 @@
         </is>
       </c>
       <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>88</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>40</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>25</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -52336,7 +52740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J519"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -52552,7 +52956,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46252.15456611976</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -54852,15 +55256,36 @@
         </is>
       </c>
       <c r="G519" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46251.15609918981</v>
       </c>
       <c r="H519" s="282" t="n">
-        <v>46251.15609919124</v>
+        <v>46251.15609918981</v>
       </c>
       <c r="I519" t="n">
         <v>4</v>
       </c>
       <c r="J519" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>RUN-20260818034234</t>
+        </is>
+      </c>
+      <c r="G520" s="282" t="n">
+        <v>46252.15456611976</v>
+      </c>
+      <c r="H520" s="282" t="n">
+        <v>46252.15456611976</v>
+      </c>
+      <c r="I520" t="n">
+        <v>4</v>
+      </c>
+      <c r="J520" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46253.15407629652</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46253.15407629652</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46253.15407629652</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46253.15407629652</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -50203,7 +50203,6 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -50236,7 +50235,6 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -50269,7 +50267,6 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -50296,6 +50293,413 @@
         </is>
       </c>
       <c r="H193" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>88</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>40</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>25</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -52740,7 +53144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -52956,7 +53360,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46253.15407629652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -55277,15 +55681,36 @@
         </is>
       </c>
       <c r="G520" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46252.15456612268</v>
       </c>
       <c r="H520" s="282" t="n">
-        <v>46252.15456611976</v>
+        <v>46252.15456612268</v>
       </c>
       <c r="I520" t="n">
         <v>4</v>
       </c>
       <c r="J520" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>RUN-20260819034152</t>
+        </is>
+      </c>
+      <c r="G521" s="282" t="n">
+        <v>46253.15407629652</v>
+      </c>
+      <c r="H521" s="282" t="n">
+        <v>46253.15407629652</v>
+      </c>
+      <c r="I521" t="n">
+        <v>4</v>
+      </c>
+      <c r="J521" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46254.15379770978</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46254.15379770978</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46254.15379770978</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46254.15379770978</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -50607,7 +50607,6 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -50640,7 +50639,6 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -50673,7 +50671,6 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -50700,6 +50697,481 @@
         </is>
       </c>
       <c r="H204" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>88</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>40</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>25</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>600</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>EPC Package with Land for Development of Grid-Connected Solar PV Projects of Aggregate Capacity up to 1000 MW in the States of Punjab and Rajasthan, i</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -53144,7 +53616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J521"/>
+  <dimension ref="A1:J522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -53360,7 +53832,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46254.15379770978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -55702,15 +56174,36 @@
         </is>
       </c>
       <c r="G521" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46253.1540762963</v>
       </c>
       <c r="H521" s="282" t="n">
-        <v>46253.15407629652</v>
+        <v>46253.1540762963</v>
       </c>
       <c r="I521" t="n">
         <v>4</v>
       </c>
       <c r="J521" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>RUN-20260820034128</t>
+        </is>
+      </c>
+      <c r="G522" s="282" t="n">
+        <v>46254.15379770978</v>
+      </c>
+      <c r="H522" s="282" t="n">
+        <v>46254.15379770978</v>
+      </c>
+      <c r="I522" t="n">
+        <v>4</v>
+      </c>
+      <c r="J522" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22858,7 +22858,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46255.15751608137</v>
       </c>
     </row>
     <row r="3">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46255.15751608137</v>
       </c>
     </row>
     <row r="4">
@@ -23163,7 +23163,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46255.15751608137</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46255.15751608137</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -51011,13 +51011,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -51043,7 +51041,6 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -51079,7 +51076,6 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -51112,7 +51108,6 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51145,7 +51140,6 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51172,6 +51166,481 @@
         </is>
       </c>
       <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>88</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>40</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>25</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>600</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>EPC Package with Land for Development of Grid-Connected Solar PV Projects of Aggregate Capacity up to 1000 MW in the States of Punjab and Rajasthan, i</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Insurance Coverage (Fire &amp; Burglary) for 571.22 MWp Solar PV Modules stored at Village Mohija Paranda, Post Kurula, Tehsil Kandhar, District Nanded, M</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -53616,7 +54085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J522"/>
+  <dimension ref="A1:J523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -53832,7 +54301,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46255.15751608137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -56195,15 +56664,36 @@
         </is>
       </c>
       <c r="G522" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46254.15379770834</v>
       </c>
       <c r="H522" s="282" t="n">
-        <v>46254.15379770978</v>
+        <v>46254.15379770834</v>
       </c>
       <c r="I522" t="n">
         <v>4</v>
       </c>
       <c r="J522" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>RUN-20260821034649</t>
+        </is>
+      </c>
+      <c r="G523" s="282" t="n">
+        <v>46255.15751608137</v>
+      </c>
+      <c r="H523" s="282" t="n">
+        <v>46255.15751608137</v>
+      </c>
+      <c r="I523" t="n">
+        <v>4</v>
+      </c>
+      <c r="J523" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22663,27 +22663,27 @@
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>SJVN-BESS2</t>
+          <t>MSEDCL-BESS-2000</t>
         </is>
       </c>
       <c r="B2" s="37" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="C2" s="37" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>MSEDCL</t>
         </is>
       </c>
       <c r="D2" s="37" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E2" s="37" t="inlineStr">
         <is>
-          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
+          <t>RfS-2000MW-4000MWh-BESS-2026</t>
         </is>
       </c>
       <c r="F2" s="37" t="inlineStr">
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="G2" s="274" t="n">
-        <v>265</v>
+        <v>2000</v>
       </c>
       <c r="H2" s="37" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="J2" s="37" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and TBCB</t>
+          <t>Tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="K2" s="274" t="n"/>
@@ -22714,31 +22714,29 @@
           <t>As per RfS</t>
         </is>
       </c>
-      <c r="N2" s="280" t="n">
-        <v>46255</v>
-      </c>
+      <c r="N2" s="280" t="n"/>
       <c r="O2" s="280" t="n"/>
       <c r="P2" s="280" t="n"/>
       <c r="Q2" s="280" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Corrigendum</t>
         </is>
       </c>
       <c r="R2" s="280" t="n">
         <v>46236</v>
       </c>
       <c r="S2" s="37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" s="37" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/en/tender</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="U2" s="37" t="n"/>
       <c r="V2" s="37" t="inlineStr">
         <is>
-          <t>265 MW / 530 MWh BESS in Haryana</t>
+          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
         </is>
       </c>
       <c r="W2" s="278">
@@ -22758,7 +22756,7 @@
         <v/>
       </c>
       <c r="AA2">
-        <f>IF(A4="","",C4&amp;"|"&amp;E4&amp;"|"&amp;TEXT(N4,"yyyymmdd")&amp;"|"&amp;Q4&amp;"|"&amp;S4&amp;"|"&amp;TEXT(AI4,"yyyymmdd"))</f>
+        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
         <v/>
       </c>
       <c r="AB2" s="281" t="n">
@@ -22771,65 +22769,71 @@
       </c>
       <c r="AD2" s="281" t="inlineStr">
         <is>
-          <t>Core fields</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="AE2" s="281">
-        <f>IF(A4="","",IF(AC4="Official agency page",3,IF(AC4="Official government portal",3,IF(AC4="Official tender document",4,1)))+IF(AD4="Core fields",2,1))</f>
+        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
         <v/>
       </c>
       <c r="AF2" s="281">
-        <f>IF(A4="","",IF(OR(Q4="Open",Q4="Extended"),"Current Opportunity",IF(Q4="Corrigendum","Needs Status Check",IF(Q4="Evaluation","Under Evaluation","Historical / Closed"))))</f>
+        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
         <v/>
       </c>
       <c r="AG2" s="281" t="n">
-        <v>46227</v>
-      </c>
-      <c r="AH2" s="281" t="n"/>
-      <c r="AI2" s="281" t="n"/>
+        <v>46203</v>
+      </c>
+      <c r="AH2" s="281" t="inlineStr">
+        <is>
+          <t>2026-07-07; 2026-07-22</t>
+        </is>
+      </c>
+      <c r="AI2" s="281" t="n">
+        <v>46225</v>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>No corrigendum identified in the captured official listing.</t>
+          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Standalone BESS under VGF and tariff-based competitive bidding</t>
+          <t>Standalone BESS under tariff-based competitive bidding</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Dispatch schedule and availability obligations governed by RfS/BESSA/BESPA</t>
+          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>PLF is not applicable to standalone BESS; monthly availability/energy obligations require document review</t>
+          <t>Monthly availability/payment condition not verified from accessible current document text</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Annual PLF/CUF not applicable; annual availability/cycle obligations require document review</t>
+          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Not verified from accessible document text</t>
+          <t>Not verified from accessible current 2026 document text</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Charging-source provision not verified from accessible document text</t>
+          <t>Charging source and grid/exchange charging permission not verified</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -22839,7 +22843,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>Official RfS PDF was listed but could not be reliably fetched in this review</t>
+          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -22849,95 +22853,81 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>https://sjvn.nic.in/sites/default/files/2026-07/RfS%20BESS%202%20240726.pdf</t>
+          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Document-level review pending; no assumptions inserted</t>
+          <t>Tender confirmed; commercial clause extraction pending</t>
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46256.1508900563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL-BESS-2000</t>
+          <t>SECI000240</t>
         </is>
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C3" s="37" t="inlineStr">
         <is>
-          <t>MSEDCL</t>
-        </is>
-      </c>
-      <c r="D3" s="37" t="inlineStr">
-        <is>
-          <t>Maharashtra</t>
-        </is>
-      </c>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="D3" s="37" t="n"/>
       <c r="E3" s="37" t="inlineStr">
         <is>
-          <t>RfS-2000MW-4000MWh-BESS-2026</t>
+          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>FDRE</t>
         </is>
       </c>
       <c r="G3" s="274" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="37" t="inlineStr">
-        <is>
-          <t>Tariff-based competitive bidding</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" s="37" t="n"/>
+      <c r="J3" s="37" t="n"/>
       <c r="K3" s="274" t="n"/>
       <c r="L3" s="37" t="n"/>
-      <c r="M3" s="37" t="inlineStr">
-        <is>
-          <t>As per RfS</t>
-        </is>
-      </c>
+      <c r="M3" s="37" t="n"/>
       <c r="N3" s="280" t="n"/>
       <c r="O3" s="280" t="n"/>
       <c r="P3" s="280" t="n"/>
       <c r="Q3" s="280" t="inlineStr">
         <is>
-          <t>Corrigendum</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="R3" s="280" t="n">
-        <v>46236</v>
+        <v>46237.26024921297</v>
       </c>
       <c r="S3" s="37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" s="37" t="inlineStr">
         <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
+          <t>https://www.seci.co.in/tender-details/YmZ3</t>
         </is>
       </c>
       <c r="U3" s="37" t="n"/>
       <c r="V3" s="37" t="inlineStr">
         <is>
-          <t>Corrigendum-2 published 22-Jul-2026; deadline not visible on listing</t>
+          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
         </is>
       </c>
       <c r="W3" s="278">
@@ -22956,120 +22946,34 @@
         <f>IF(Y3="","",IF(COUNTIF($Y$2:$Y$501,Y3)&gt;1,"Duplicate","Unique"))</f>
         <v/>
       </c>
-      <c r="AA3">
-        <f>IF(A5="","",C5&amp;"|"&amp;E5&amp;"|"&amp;TEXT(N5,"yyyymmdd")&amp;"|"&amp;Q5&amp;"|"&amp;S5&amp;"|"&amp;TEXT(AI5,"yyyymmdd"))</f>
-        <v/>
-      </c>
-      <c r="AB3" s="281" t="n">
-        <v>46236</v>
-      </c>
+      <c r="AB3" s="281" t="n"/>
       <c r="AC3" s="281" t="inlineStr">
         <is>
           <t>Official agency page</t>
         </is>
       </c>
-      <c r="AD3" s="281" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="AE3" s="281">
-        <f>IF(A5="","",IF(AC5="Official agency page",3,IF(AC5="Official government portal",3,IF(AC5="Official tender document",4,1)))+IF(AD5="Core fields",2,1))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="281">
-        <f>IF(A5="","",IF(OR(Q5="Open",Q5="Extended"),"Current Opportunity",IF(Q5="Corrigendum","Needs Status Check",IF(Q5="Evaluation","Under Evaluation","Historical / Closed"))))</f>
-        <v/>
-      </c>
-      <c r="AG3" s="281" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AH3" s="281" t="inlineStr">
-        <is>
-          <t>2026-07-07; 2026-07-22</t>
-        </is>
-      </c>
-      <c r="AI3" s="281" t="n">
-        <v>46225</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Addendum-1 and Addendum-2 published 07-Jul-2026; Corrigendum-2 published 22-Jul-2026</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Standalone BESS under tariff-based competitive bidding</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Dispatch/charging schedule governed by RfS and BESPA</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>PLF is not applicable to standalone BESS; daily cycle and availability obligations require current 2026 RfS review</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Monthly availability/payment condition not verified from accessible current document text</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Annual PLF/CUF not applicable; annual availability requirement not verified</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Not verified from accessible current 2026 document text</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>Charging source and grid/exchange charging permission not verified</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>Current 2026 tender and corrigenda are visible on MSEDCL, but detailed clauses require opening the RfS/corrigendum PDF</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Merchant-use rights not verified</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>https://www.mahadiscom.in/en/supplier/tenders/</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Tender confirmed; commercial clause extraction pending</t>
-        </is>
+      <c r="AD3" s="281" t="n"/>
+      <c r="AE3" s="281" t="n"/>
+      <c r="AF3" s="281" t="n"/>
+      <c r="AG3" s="281" t="n"/>
+      <c r="AH3" s="281" t="n"/>
+      <c r="AI3" s="281" t="n"/>
+      <c r="AX3" s="282" t="n">
+        <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46256.1508900563</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>SECI000240</t>
+          <t>SECI000258</t>
         </is>
       </c>
       <c r="B4" s="37" t="inlineStr">
@@ -23085,7 +22989,7 @@
       <c r="D4" s="37" t="n"/>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>SECI/C&amp;P/IPP/13/0020/25-26</t>
+          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
@@ -23094,14 +22998,16 @@
         </is>
       </c>
       <c r="G4" s="274" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" s="37" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="n">
+        <v>4</v>
+      </c>
       <c r="J4" s="37" t="n"/>
       <c r="K4" s="274" t="n"/>
       <c r="L4" s="37" t="n"/>
@@ -23115,20 +23021,20 @@
         </is>
       </c>
       <c r="R4" s="280" t="n">
-        <v>46237.26024921297</v>
+        <v>46243.17686518518</v>
       </c>
       <c r="S4" s="37" t="n">
         <v>0</v>
       </c>
       <c r="T4" s="37" t="inlineStr">
         <is>
-          <t>https://www.seci.co.in/tender-details/YmZ3</t>
+          <t>https://www.seci.co.in/tender-details/Ymd_</t>
         </is>
       </c>
       <c r="U4" s="37" t="n"/>
       <c r="V4" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details  | SECI000240 | SECI-2026-TN000004 | SECI/C&amp;P/IPP/13/0020/25-26 | RfS for Supply of 1000 MW Firm and Dispatchable Renewable Energy Round-the-Clock (FDRE-RTC) Power from ISTS-Connected RE Power Projects in India (SECI-FDRE-RTC-V) | 10/03/2026 | 20/07/2026 | View Details</t>
+          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
         </is>
       </c>
       <c r="W4" s="278">
@@ -23157,58 +23063,30 @@
       <c r="AE4" s="281" t="n"/>
       <c r="AF4" s="281" t="n"/>
       <c r="AG4" s="281" t="n"/>
-      <c r="AH4" s="281" t="n"/>
+      <c r="AH4" s="281" t="inlineStr"/>
       <c r="AI4" s="281" t="n"/>
       <c r="AX4" s="282" t="n">
-        <v>46237.26024921297</v>
+        <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46256.1508900563</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>014f0276d0bedb946c97bc1d31fd766e19a14673016f74b3288a3d56aab0e824</t>
+          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>SECI000258</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C5" s="37" t="inlineStr">
-        <is>
-          <t>SECI</t>
-        </is>
-      </c>
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>SECI/C&amp;P/IPP/13/0006/26-27</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>FDRE</t>
-        </is>
-      </c>
-      <c r="G5" s="274" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H5" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="n">
-        <v>4</v>
-      </c>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="274" t="n"/>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="37" t="n"/>
       <c r="J5" s="37" t="n"/>
       <c r="K5" s="274" t="n"/>
       <c r="L5" s="37" t="n"/>
@@ -23216,67 +23094,23 @@
       <c r="N5" s="280" t="n"/>
       <c r="O5" s="280" t="n"/>
       <c r="P5" s="280" t="n"/>
-      <c r="Q5" s="280" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R5" s="280" t="n">
-        <v>46243.17686518518</v>
-      </c>
-      <c r="S5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="37" t="inlineStr">
-        <is>
-          <t>https://www.seci.co.in/tender-details/Ymd_</t>
-        </is>
-      </c>
+      <c r="Q5" s="280" t="n"/>
+      <c r="R5" s="280" t="n"/>
+      <c r="S5" s="37" t="n"/>
+      <c r="T5" s="37" t="n"/>
       <c r="U5" s="37" t="n"/>
-      <c r="V5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details  | SECI000258 | SECI-2026-TN000014 | SECI/C&amp;P/IPP/13/0006/26-27 | RfS for assured Peak Supply of 6000 MWh (1500 MW x 4 Hrs.) from ISTS-Connected RE Projects (SECI-FDRE-IX) | 05/06/2026 | 07/08/2026 | View Details</t>
-        </is>
-      </c>
-      <c r="W5" s="278">
-        <f>IF(N5="","",N5-TODAY())</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>IF(W5="","",IF(W5&lt;0,"Expired",IF(W5&lt;=3,"Urgent",IF(W5&lt;=7,"Due in 7 Days","Normal"))))</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>UPPER(TRIM(C5&amp;"|"&amp;E5))</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>IF(Y5="","",IF(COUNTIF($Y$2:$Y$501,Y5)&gt;1,"Duplicate","Unique"))</f>
-        <v/>
-      </c>
+      <c r="V5" s="37" t="n"/>
+      <c r="W5" s="278" t="n"/>
       <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="inlineStr">
-        <is>
-          <t>Official agency page</t>
-        </is>
-      </c>
+      <c r="AC5" s="281" t="n"/>
       <c r="AD5" s="281" t="n"/>
       <c r="AE5" s="281" t="n"/>
       <c r="AF5" s="281" t="n"/>
       <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="inlineStr"/>
+      <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
-      <c r="AX5" s="282" t="n">
-        <v>46243.17686518518</v>
-      </c>
-      <c r="AY5" s="282" t="n">
-        <v>46255.15751608137</v>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>63f0892f32e39002cd45d1e3a78c55637433070adc204427287bd864299eff80</t>
-        </is>
-      </c>
+      <c r="AX5" s="282" t="n"/>
+      <c r="AY5" s="282" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="37" t="n"/>
@@ -43259,7 +43093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -51480,13 +51314,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -51512,7 +51344,6 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -51548,7 +51379,6 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -51581,7 +51411,6 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51614,7 +51443,6 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51643,6 +51471,488 @@
       <c r="H230" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>88</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>40</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>25</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>600</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>EPC Package with Land for Development of Grid-Connected Solar PV Projects of Aggregate Capacity up to 1000 MW in the States of Punjab and Rajasthan, i</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SJVN-BESS2</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SJVN/CCDelhi/REIA/2026/BESS-2</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>265</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Deadline expired without verified extension</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://sjvn.nic.in/en/tender</t>
         </is>
       </c>
     </row>
@@ -54085,7 +54395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J523"/>
+  <dimension ref="A1:J524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -54301,7 +54611,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46256.1508900563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -56685,15 +56995,36 @@
         </is>
       </c>
       <c r="G523" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46255.15751607639</v>
       </c>
       <c r="H523" s="282" t="n">
-        <v>46255.15751608137</v>
+        <v>46255.15751607639</v>
       </c>
       <c r="I523" t="n">
         <v>4</v>
       </c>
       <c r="J523" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>RUN-20260822033716</t>
+        </is>
+      </c>
+      <c r="G524" s="282" t="n">
+        <v>46256.1508900563</v>
+      </c>
+      <c r="H524" s="282" t="n">
+        <v>46256.1508900563</v>
+      </c>
+      <c r="I524" t="n">
+        <v>3</v>
+      </c>
+      <c r="J524" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46257.1571536125</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46257.1571536125</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23063,13 +23063,13 @@
       <c r="AE4" s="281" t="n"/>
       <c r="AF4" s="281" t="n"/>
       <c r="AG4" s="281" t="n"/>
-      <c r="AH4" s="281" t="inlineStr"/>
+      <c r="AH4" s="281" t="n"/>
       <c r="AI4" s="281" t="n"/>
       <c r="AX4" s="282" t="n">
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46257.1571536125</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -51783,13 +51783,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -51815,7 +51813,6 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
           <t>SJVN</t>
@@ -51851,7 +51848,6 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51884,7 +51880,6 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -51953,6 +51948,412 @@
       <c r="H243" t="inlineStr">
         <is>
           <t>https://sjvn.nic.in/en/tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>88</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>40</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>25</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>600</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
       </c>
     </row>
@@ -54395,7 +54796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J524"/>
+  <dimension ref="A1:J525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -54611,7 +55012,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46257.1571536125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57016,15 +57417,36 @@
         </is>
       </c>
       <c r="G524" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46256.15089005787</v>
       </c>
       <c r="H524" s="282" t="n">
-        <v>46256.1508900563</v>
+        <v>46256.15089005787</v>
       </c>
       <c r="I524" t="n">
         <v>3</v>
       </c>
       <c r="J524" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>RUN-20260823034618</t>
+        </is>
+      </c>
+      <c r="G525" s="282" t="n">
+        <v>46257.1571536125</v>
+      </c>
+      <c r="H525" s="282" t="n">
+        <v>46257.1571536125</v>
+      </c>
+      <c r="I525" t="n">
+        <v>3</v>
+      </c>
+      <c r="J525" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46258.1585342785</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46258.1585342785</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46258.1585342785</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -52260,13 +52260,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -52292,7 +52290,6 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -52325,7 +52322,6 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -52352,6 +52348,412 @@
         </is>
       </c>
       <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>88</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>40</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>25</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>600</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -54796,7 +55198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J525"/>
+  <dimension ref="A1:J526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -55012,7 +55414,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46258.1585342785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57438,15 +57840,36 @@
         </is>
       </c>
       <c r="G525" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46257.15715361111</v>
       </c>
       <c r="H525" s="282" t="n">
-        <v>46257.1571536125</v>
+        <v>46257.15715361111</v>
       </c>
       <c r="I525" t="n">
         <v>3</v>
       </c>
       <c r="J525" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>RUN-20260824034817</t>
+        </is>
+      </c>
+      <c r="G526" s="282" t="n">
+        <v>46258.1585342785</v>
+      </c>
+      <c r="H526" s="282" t="n">
+        <v>46258.1585342785</v>
+      </c>
+      <c r="I526" t="n">
+        <v>3</v>
+      </c>
+      <c r="J526" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46259.15922154199</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46259.15922154199</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46259.15922154199</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -52662,13 +52662,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -52694,7 +52692,6 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -52727,7 +52724,6 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -52754,6 +52750,412 @@
         </is>
       </c>
       <c r="H265" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>88</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>25</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>40</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>600</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -55198,7 +55600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J526"/>
+  <dimension ref="A1:J527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -55414,7 +55816,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46259.15922154199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57861,15 +58263,36 @@
         </is>
       </c>
       <c r="G526" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46258.15853428241</v>
       </c>
       <c r="H526" s="282" t="n">
-        <v>46258.1585342785</v>
+        <v>46258.15853428241</v>
       </c>
       <c r="I526" t="n">
         <v>3</v>
       </c>
       <c r="J526" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>RUN-20260825034916</t>
+        </is>
+      </c>
+      <c r="G527" s="282" t="n">
+        <v>46259.15922154199</v>
+      </c>
+      <c r="H527" s="282" t="n">
+        <v>46259.15922154199</v>
+      </c>
+      <c r="I527" t="n">
+        <v>3</v>
+      </c>
+      <c r="J527" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46260.16136023542</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46260.16136023542</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46260.16136023542</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -53064,13 +53064,11 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -53096,7 +53094,6 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -53129,7 +53126,6 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -53156,6 +53152,412 @@
         </is>
       </c>
       <c r="H276" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>88</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>25</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>40</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>600</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -55600,7 +56002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J527"/>
+  <dimension ref="A1:J528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -55816,7 +56218,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46260.16136023542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -58284,15 +58686,36 @@
         </is>
       </c>
       <c r="G527" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46259.15922153935</v>
       </c>
       <c r="H527" s="282" t="n">
-        <v>46259.15922154199</v>
+        <v>46259.15922153935</v>
       </c>
       <c r="I527" t="n">
         <v>3</v>
       </c>
       <c r="J527" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>RUN-20260826035221</t>
+        </is>
+      </c>
+      <c r="G528" s="282" t="n">
+        <v>46260.16136023542</v>
+      </c>
+      <c r="H528" s="282" t="n">
+        <v>46260.16136023542</v>
+      </c>
+      <c r="I528" t="n">
+        <v>3</v>
+      </c>
+      <c r="J528" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46261.55242623287</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46261.55242623287</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46261.55242623287</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23079,14 +23079,34 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="n"/>
-      <c r="B5" s="37" t="n"/>
-      <c r="C5" s="37" t="n"/>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="37" t="n"/>
-      <c r="F5" s="37" t="n"/>
-      <c r="G5" s="274" t="n"/>
-      <c r="H5" s="37" t="n"/>
-      <c r="I5" s="37" t="n"/>
+      <c r="E5" s="37" t="inlineStr"/>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="G5" s="274" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>12</v>
+      </c>
       <c r="J5" s="37" t="n"/>
       <c r="K5" s="274" t="n"/>
       <c r="L5" s="37" t="n"/>
@@ -23094,23 +23114,66 @@
       <c r="N5" s="280" t="n"/>
       <c r="O5" s="280" t="n"/>
       <c r="P5" s="280" t="n"/>
-      <c r="Q5" s="280" t="n"/>
-      <c r="R5" s="280" t="n"/>
+      <c r="Q5" s="280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R5" s="280" t="n">
+        <v>46261.55242623287</v>
+      </c>
       <c r="S5" s="37" t="n"/>
-      <c r="T5" s="37" t="n"/>
-      <c r="U5" s="37" t="n"/>
-      <c r="V5" s="37" t="n"/>
-      <c r="W5" s="278" t="n"/>
+      <c r="T5" s="37" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30195</t>
+        </is>
+      </c>
+      <c r="U5" s="37" t="inlineStr"/>
+      <c r="V5" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  | GEM/2026/B/7937631 |  | Hiring of Latest Model of Mahindra Scorpio (4 WD) or equivalent 4WD Not earlier than 2026 Make)
+vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 | </t>
+        </is>
+      </c>
+      <c r="W5" s="278">
+        <f>IF(N5="","",N5-TODAY())</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>IF(W5="","",IF(W5&lt;0,"Expired",IF(W5&lt;=3,"Urgent",IF(W5&lt;=7,"Due in 7 Days","Normal"))))</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>UPPER(TRIM(C5&amp;"|"&amp;E5))</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>IF(Y5="","",IF(COUNTIF($Y$2:$Y$501,Y5)&gt;1,"Duplicate","Unique"))</f>
+        <v/>
+      </c>
       <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
+      <c r="AC5" s="281" t="inlineStr">
+        <is>
+          <t>Official agency page</t>
+        </is>
+      </c>
       <c r="AD5" s="281" t="n"/>
       <c r="AE5" s="281" t="n"/>
       <c r="AF5" s="281" t="n"/>
       <c r="AG5" s="281" t="n"/>
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
-      <c r="AX5" s="282" t="n"/>
-      <c r="AY5" s="282" t="n"/>
+      <c r="AX5" s="282" t="n">
+        <v>46261.55242623287</v>
+      </c>
+      <c r="AY5" s="282" t="n">
+        <v>46261.55242623287</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>286d8b8b38453495f5738007073f35031778ce3f4a241b150680a5fe26d93a05</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="37" t="n"/>
@@ -43093,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -53466,13 +53529,11 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -53498,7 +53559,6 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -53531,7 +53591,6 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -53558,6 +53617,412 @@
         </is>
       </c>
       <c r="H287" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>88</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>25</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>40</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>600</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -56002,7 +56467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J528"/>
+  <dimension ref="A1:J529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -56218,7 +56683,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46261.55242623287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -58707,15 +59172,36 @@
         </is>
       </c>
       <c r="G528" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46260.16136023148</v>
       </c>
       <c r="H528" s="282" t="n">
-        <v>46260.16136023542</v>
+        <v>46260.16136023148</v>
       </c>
       <c r="I528" t="n">
         <v>3</v>
       </c>
       <c r="J528" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>RUN-20260827131529</t>
+        </is>
+      </c>
+      <c r="G529" s="282" t="n">
+        <v>46261.55242623287</v>
+      </c>
+      <c r="H529" s="282" t="n">
+        <v>46261.55242623287</v>
+      </c>
+      <c r="I529" t="n">
+        <v>4</v>
+      </c>
+      <c r="J529" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -53931,13 +53931,11 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -53963,7 +53961,6 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -53996,7 +53993,6 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -54023,6 +54019,489 @@
         </is>
       </c>
       <c r="H298" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>50</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>88</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>25</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>40</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>600</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -56467,7 +56946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J529"/>
+  <dimension ref="A1:J530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -56683,7 +57162,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46262.62463509951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -59193,15 +59672,36 @@
         </is>
       </c>
       <c r="G529" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46261.55242623843</v>
       </c>
       <c r="H529" s="282" t="n">
-        <v>46261.55242623287</v>
+        <v>46261.55242623843</v>
       </c>
       <c r="I529" t="n">
         <v>4</v>
       </c>
       <c r="J529" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>RUN-20260828145928</t>
+        </is>
+      </c>
+      <c r="G530" s="282" t="n">
+        <v>46262.62463509951</v>
+      </c>
+      <c r="H530" s="282" t="n">
+        <v>46262.62463509951</v>
+      </c>
+      <c r="I530" t="n">
+        <v>4</v>
+      </c>
+      <c r="J530" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H311"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -54410,13 +54410,11 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -54442,7 +54440,6 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -54475,7 +54472,6 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -54502,6 +54498,489 @@
         </is>
       </c>
       <c r="H311" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>50</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>88</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>25</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>40</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>600</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Supply / installation excluded</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -56946,7 +57425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J530"/>
+  <dimension ref="A1:J531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -57162,7 +57641,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46263.40839206373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -59693,15 +60172,36 @@
         </is>
       </c>
       <c r="G530" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46262.62463510417</v>
       </c>
       <c r="H530" s="282" t="n">
-        <v>46262.62463509951</v>
+        <v>46262.62463510417</v>
       </c>
       <c r="I530" t="n">
         <v>4</v>
       </c>
       <c r="J530" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>RUN-20260829094805</t>
+        </is>
+      </c>
+      <c r="G531" s="282" t="n">
+        <v>46263.40839206373</v>
+      </c>
+      <c r="H531" s="282" t="n">
+        <v>46263.40839206373</v>
+      </c>
+      <c r="I531" t="n">
+        <v>4</v>
+      </c>
+      <c r="J531" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -54889,13 +54889,11 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>Wind</t>
@@ -54921,7 +54919,6 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -54954,7 +54951,6 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -54981,6 +54977,457 @@
         </is>
       </c>
       <c r="H324" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>50</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>88</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>25</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>40</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -57425,7 +57872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J531"/>
+  <dimension ref="A1:J532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -57641,7 +58088,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46264.36455835657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -60193,15 +60640,36 @@
         </is>
       </c>
       <c r="G531" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46263.40839206018</v>
       </c>
       <c r="H531" s="282" t="n">
-        <v>46263.40839206373</v>
+        <v>46263.40839206018</v>
       </c>
       <c r="I531" t="n">
         <v>4</v>
       </c>
       <c r="J531" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>RUN-20260830084457</t>
+        </is>
+      </c>
+      <c r="G532" s="282" t="n">
+        <v>46264.36455835657</v>
+      </c>
+      <c r="H532" s="282" t="n">
+        <v>46264.36455835657</v>
+      </c>
+      <c r="I532" t="n">
+        <v>4</v>
+      </c>
+      <c r="J532" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H336"/>
+  <dimension ref="A1:H348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -55368,7 +55368,6 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -55401,7 +55400,6 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -55428,6 +55426,457 @@
         </is>
       </c>
       <c r="H336" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>50</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>88</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>25</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>40</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -57872,7 +58321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -58088,7 +58537,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46265.37876917262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -60661,15 +61110,36 @@
         </is>
       </c>
       <c r="G532" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46264.36455835648</v>
       </c>
       <c r="H532" s="282" t="n">
-        <v>46264.36455835657</v>
+        <v>46264.36455835648</v>
       </c>
       <c r="I532" t="n">
         <v>4</v>
       </c>
       <c r="J532" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>RUN-20260831090525</t>
+        </is>
+      </c>
+      <c r="G533" s="282" t="n">
+        <v>46265.37876917262</v>
+      </c>
+      <c r="H533" s="282" t="n">
+        <v>46265.37876917262</v>
+      </c>
+      <c r="I533" t="n">
+        <v>4</v>
+      </c>
+      <c r="J533" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H348"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -55817,7 +55817,6 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -55850,7 +55849,6 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -55877,6 +55875,457 @@
         </is>
       </c>
       <c r="H348" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>50</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>88</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>25</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>40</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -58321,7 +58770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J533"/>
+  <dimension ref="A1:J534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -58537,7 +58986,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46266.34220822147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -61131,15 +61580,36 @@
         </is>
       </c>
       <c r="G533" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46265.37876917824</v>
       </c>
       <c r="H533" s="282" t="n">
-        <v>46265.37876917262</v>
+        <v>46265.37876917824</v>
       </c>
       <c r="I533" t="n">
         <v>4</v>
       </c>
       <c r="J533" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>RUN-20260901081246</t>
+        </is>
+      </c>
+      <c r="G534" s="282" t="n">
+        <v>46266.34220822147</v>
+      </c>
+      <c r="H534" s="282" t="n">
+        <v>46266.34220822147</v>
+      </c>
+      <c r="I534" t="n">
+        <v>4</v>
+      </c>
+      <c r="J534" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H360"/>
+  <dimension ref="A1:H372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -56266,7 +56266,6 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -56299,7 +56298,6 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -56326,6 +56324,457 @@
         </is>
       </c>
       <c r="H360" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>50</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>88</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>25</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>40</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>View Details Tender Document Addendum-I Pre-Bid Meeting Link Corrigendum-II Addendum-6 Odisha Floating Solar Data Room - Contents Addendum_09 Addendum</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Corrigendum</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://www.gridco.co.in/writereaddata/Tenders/301225101225upload.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>GRIDCO</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Addendum-6 Odisha Floating Solar Data Room - Contents</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
         </is>
@@ -58770,7 +59219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J534"/>
+  <dimension ref="A1:J535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -58986,7 +59435,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46267.3141819641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -61601,15 +62050,36 @@
         </is>
       </c>
       <c r="G534" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46266.34220821759</v>
       </c>
       <c r="H534" s="282" t="n">
-        <v>46266.34220822147</v>
+        <v>46266.34220821759</v>
       </c>
       <c r="I534" t="n">
         <v>4</v>
       </c>
       <c r="J534" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>RUN-20260902073225</t>
+        </is>
+      </c>
+      <c r="G535" s="282" t="n">
+        <v>46267.3141819641</v>
+      </c>
+      <c r="H535" s="282" t="n">
+        <v>46267.3141819641</v>
+      </c>
+      <c r="I535" t="n">
+        <v>4</v>
+      </c>
+      <c r="J535" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
@@ -23164,10 +23164,10 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H372"/>
+  <dimension ref="A1:H382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -56715,7 +56715,6 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -56748,7 +56747,6 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
           <t>GRIDCO</t>
@@ -56777,6 +56775,391 @@
       <c r="H372" t="inlineStr">
         <is>
           <t>https://www.gridco.co.in/writereaddata/Tenders/301126051106Addendum-6_Odisha Floating Solar Data room - Contents.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>50</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>88</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>25</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>40</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
         </is>
       </c>
     </row>
@@ -59219,7 +59602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J535"/>
+  <dimension ref="A1:J536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -59435,7 +59818,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46268.31632459372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -62071,15 +62454,36 @@
         </is>
       </c>
       <c r="G535" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46267.31418196759</v>
       </c>
       <c r="H535" s="282" t="n">
-        <v>46267.3141819641</v>
+        <v>46267.31418196759</v>
       </c>
       <c r="I535" t="n">
         <v>4</v>
       </c>
       <c r="J535" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>RUN-20260903073530</t>
+        </is>
+      </c>
+      <c r="G536" s="282" t="n">
+        <v>46268.31632459372</v>
+      </c>
+      <c r="H536" s="282" t="n">
+        <v>46268.31632459372</v>
+      </c>
+      <c r="I536" t="n">
+        <v>4</v>
+      </c>
+      <c r="J536" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23078,7 +23078,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="n"/>
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>SECI000278</t>
+        </is>
+      </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Central</t>
@@ -23086,27 +23090,29 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>NTPC REL</t>
+          <t>SECI</t>
         </is>
       </c>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="37" t="inlineStr"/>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0009/26-27</t>
+        </is>
+      </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
       <c r="G5" s="274" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="n">
-        <v>12</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="n"/>
       <c r="J5" s="37" t="n"/>
       <c r="K5" s="274" t="n"/>
       <c r="L5" s="37" t="n"/>
@@ -23120,19 +23126,18 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="S5" s="37" t="n"/>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30195</t>
+          <t>https://www.seci.co.in/tender-details/YmV_</t>
         </is>
       </c>
       <c r="U5" s="37" t="inlineStr"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  | GEM/2026/B/7937631 |  | Hiring of Latest Model of Mahindra Scorpio (4 WD) or equivalent 4WD Not earlier than 2026 Make)
-vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 | </t>
+          <t xml:space="preserve"> | SECI000278 | SECI-2026-TN000027 | SECI/C&amp;P/IPP/15/0009/26-27 | 700 MW ISTS-Connected Solar PV Power Projects in India under TBCB (C&amp;I-1) | 03/09/2026 | 05/10/2026 | View Details  | SECI000278 | SECI-2026-TN000027 | SECI/C&amp;P/IPP/15/0009/26-27 | 700 MW ISTS-Connected Solar PV Power Projects in India under TBCB (C&amp;I-1) | 03/09/2026 | 05/10/2026 | View Details</t>
         </is>
       </c>
       <c r="W5" s="278">
@@ -23164,27 +23169,47 @@
       <c r="AH5" s="281" t="n"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>286d8b8b38453495f5738007073f35031778ce3f4a241b150680a5fe26d93a05</t>
+          <t>d786aacd56a0030d39fc6bd03bae43162dd514bad824c5c2ceb3f926c8fcb952</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="37" t="n"/>
-      <c r="B6" s="37" t="n"/>
-      <c r="C6" s="37" t="n"/>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
       <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-      <c r="G6" s="274" t="n"/>
-      <c r="H6" s="37" t="n"/>
-      <c r="I6" s="37" t="n"/>
+      <c r="E6" s="37" t="inlineStr"/>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="G6" s="274" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" s="37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="n">
+        <v>12</v>
+      </c>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="274" t="n"/>
       <c r="L6" s="37" t="n"/>
@@ -23192,23 +23217,66 @@
       <c r="N6" s="280" t="n"/>
       <c r="O6" s="280" t="n"/>
       <c r="P6" s="280" t="n"/>
-      <c r="Q6" s="280" t="n"/>
-      <c r="R6" s="280" t="n"/>
+      <c r="Q6" s="280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R6" s="280" t="n">
+        <v>46269.31819382161</v>
+      </c>
       <c r="S6" s="37" t="n"/>
-      <c r="T6" s="37" t="n"/>
-      <c r="U6" s="37" t="n"/>
-      <c r="V6" s="37" t="n"/>
-      <c r="W6" s="278" t="n"/>
+      <c r="T6" s="37" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30195</t>
+        </is>
+      </c>
+      <c r="U6" s="37" t="inlineStr"/>
+      <c r="V6" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  | GEM/2026/B/7937631 |  | Hiring of Latest Model of Mahindra Scorpio (4 WD) or equivalent 4WD Not earlier than 2026 Make)
+vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 | </t>
+        </is>
+      </c>
+      <c r="W6" s="278">
+        <f>IF(N6="","",N6-TODAY())</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>IF(W6="","",IF(W6&lt;0,"Expired",IF(W6&lt;=3,"Urgent",IF(W6&lt;=7,"Due in 7 Days","Normal"))))</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>UPPER(TRIM(C6&amp;"|"&amp;E6))</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>IF(Y6="","",IF(COUNTIF($Y$2:$Y$501,Y6)&gt;1,"Duplicate","Unique"))</f>
+        <v/>
+      </c>
       <c r="AB6" s="281" t="n"/>
-      <c r="AC6" s="281" t="n"/>
+      <c r="AC6" s="281" t="inlineStr">
+        <is>
+          <t>Official agency page</t>
+        </is>
+      </c>
       <c r="AD6" s="281" t="n"/>
       <c r="AE6" s="281" t="n"/>
       <c r="AF6" s="281" t="n"/>
       <c r="AG6" s="281" t="n"/>
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
-      <c r="AX6" s="282" t="n"/>
-      <c r="AY6" s="282" t="n"/>
+      <c r="AX6" s="282" t="n">
+        <v>46269.31819382161</v>
+      </c>
+      <c r="AY6" s="282" t="n">
+        <v>46269.31819382161</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>286d8b8b38453495f5738007073f35031778ce3f4a241b150680a5fe26d93a05</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="37" t="n"/>
@@ -43156,7 +43224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H382"/>
+  <dimension ref="A1:H393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -57160,6 +57228,420 @@
       <c r="H382" t="inlineStr">
         <is>
           <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>50</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>25</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>88</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>40</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
         </is>
       </c>
     </row>
@@ -59602,7 +60084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J536"/>
+  <dimension ref="A1:J537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -59818,7 +60300,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46269.31819382161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -62475,15 +62957,36 @@
         </is>
       </c>
       <c r="G536" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46268.31632459491</v>
       </c>
       <c r="H536" s="282" t="n">
-        <v>46268.31632459372</v>
+        <v>46268.31632459491</v>
       </c>
       <c r="I536" t="n">
         <v>4</v>
       </c>
       <c r="J536" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>RUN-20260904073811</t>
+        </is>
+      </c>
+      <c r="G537" s="282" t="n">
+        <v>46269.31819382161</v>
+      </c>
+      <c r="H537" s="282" t="n">
+        <v>46269.31819382161</v>
+      </c>
+      <c r="I537" t="n">
+        <v>5</v>
+      </c>
+      <c r="J537" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23126,15 +23126,17 @@
         </is>
       </c>
       <c r="R5" s="280" t="n">
-        <v>46269.31819382161</v>
-      </c>
-      <c r="S5" s="37" t="n"/>
+        <v>46269.31819381945</v>
+      </c>
+      <c r="S5" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" s="37" t="inlineStr">
         <is>
           <t>https://www.seci.co.in/tender-details/YmV_</t>
         </is>
       </c>
-      <c r="U5" s="37" t="inlineStr"/>
+      <c r="U5" s="37" t="n"/>
       <c r="V5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> | SECI000278 | SECI-2026-TN000027 | SECI/C&amp;P/IPP/15/0009/26-27 | 700 MW ISTS-Connected Solar PV Power Projects in India under TBCB (C&amp;I-1) | 03/09/2026 | 05/10/2026 | View Details  | SECI000278 | SECI-2026-TN000027 | SECI/C&amp;P/IPP/15/0009/26-27 | 700 MW ISTS-Connected Solar PV Power Projects in India under TBCB (C&amp;I-1) | 03/09/2026 | 05/10/2026 | View Details</t>
@@ -23166,13 +23168,13 @@
       <c r="AE5" s="281" t="n"/>
       <c r="AF5" s="281" t="n"/>
       <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
+      <c r="AH5" s="281" t="inlineStr"/>
       <c r="AI5" s="281" t="n"/>
       <c r="AX5" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46269.31819381945</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23223,7 +23225,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23267,10 +23269,10 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -43224,7 +43226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H393"/>
+  <dimension ref="A1:H404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -57617,13 +57619,11 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>Other</t>
@@ -57640,6 +57640,420 @@
         </is>
       </c>
       <c r="H393" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>50</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>25</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>88</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>40</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
         <is>
           <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
         </is>
@@ -60084,7 +60498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J537"/>
+  <dimension ref="A1:J538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -60300,7 +60714,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46270.30568661663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -62978,15 +63392,36 @@
         </is>
       </c>
       <c r="G537" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46269.31819381945</v>
       </c>
       <c r="H537" s="282" t="n">
-        <v>46269.31819382161</v>
+        <v>46269.31819381945</v>
       </c>
       <c r="I537" t="n">
         <v>5</v>
       </c>
       <c r="J537" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>RUN-20260905072011</t>
+        </is>
+      </c>
+      <c r="G538" s="282" t="n">
+        <v>46270.30568661663</v>
+      </c>
+      <c r="H538" s="282" t="n">
+        <v>46270.30568661663</v>
+      </c>
+      <c r="I538" t="n">
+        <v>5</v>
+      </c>
+      <c r="J538" t="inlineStr">
         <is>
           <t>Success</t>
         </is>

--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46269.31819381945</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23237,7 +23237,7 @@
       <c r="V6" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  | GEM/2026/B/7937631 |  | Hiring of Latest Model of Mahindra Scorpio (4 WD) or equivalent 4WD Not earlier than 2026 Make)
-vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 | </t>
+vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 1 day to go | </t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23269,14 +23269,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>286d8b8b38453495f5738007073f35031778ce3f4a241b150680a5fe26d93a05</t>
+          <t>f3237a45e074d1244d8137eec1934d44417cb404ec6db3244f0b76b687b7dfff</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H404"/>
+  <dimension ref="A1:H415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -58031,13 +58031,11 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>Other</t>
@@ -58054,6 +58052,420 @@
         </is>
       </c>
       <c r="H404" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>50</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>25</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>88</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>40</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
         <is>
           <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
         </is>
@@ -60498,7 +60910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J538"/>
+  <dimension ref="A1:J539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -60714,7 +61126,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46271.31189353833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -63413,15 +63825,36 @@
         </is>
       </c>
       <c r="G538" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46270.30568662037</v>
       </c>
       <c r="H538" s="282" t="n">
-        <v>46270.30568661663</v>
+        <v>46270.30568662037</v>
       </c>
       <c r="I538" t="n">
         <v>5</v>
       </c>
       <c r="J538" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>RUN-20260906072907</t>
+        </is>
+      </c>
+      <c r="G539" s="282" t="n">
+        <v>46271.31189353833</v>
+      </c>
+      <c r="H539" s="282" t="n">
+        <v>46271.31189353833</v>
+      </c>
+      <c r="I539" t="n">
+        <v>5</v>
+      </c>
+      <c r="J539" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
